--- a/02.26_Estrutura Integra 6A _cleulton fevereiro.xlsx
+++ b/02.26_Estrutura Integra 6A _cleulton fevereiro.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40E1CB0E-34BA-4521-8A20-77F59BB4B0B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EBC3398-1FB7-460D-A5E9-E061E7E6A8EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5826" uniqueCount="753">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5825" uniqueCount="752">
   <si>
     <t>setor</t>
   </si>
@@ -2292,9 +2292,6 @@
   </si>
   <si>
     <t>Provisões - 13º + Férias</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -2327,12 +2324,36 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -2363,7 +2384,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -2371,8 +2392,11 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2697,7 +2721,7 @@
     <col min="5" max="5" width="13.44140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="39.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="34.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="19" customWidth="1"/>
     <col min="10" max="10" width="11" customWidth="1"/>
     <col min="11" max="11" width="13.44140625" customWidth="1"/>
     <col min="12" max="13" width="22.77734375" customWidth="1"/>
@@ -2706,7 +2730,7 @@
     <col min="16" max="16" width="19.77734375" customWidth="1" outlineLevel="1"/>
     <col min="17" max="17" width="18.88671875" customWidth="1" outlineLevel="1"/>
     <col min="18" max="18" width="25.77734375" customWidth="1" outlineLevel="1"/>
-    <col min="19" max="19" width="15" bestFit="1" customWidth="1" outlineLevel="1"/>
+    <col min="19" max="19" width="15" customWidth="1" outlineLevel="1"/>
     <col min="20" max="20" width="17.21875" customWidth="1"/>
     <col min="21" max="21" width="16.88671875" customWidth="1"/>
     <col min="22" max="22" width="16" customWidth="1"/>
@@ -2720,7 +2744,7 @@
     <col min="30" max="30" width="21.77734375" customWidth="1"/>
     <col min="31" max="31" width="17.6640625" customWidth="1"/>
     <col min="32" max="32" width="15.109375" customWidth="1"/>
-    <col min="33" max="33" width="15" customWidth="1"/>
+    <col min="33" max="33" width="20.5546875" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="13.77734375" customWidth="1"/>
     <col min="35" max="35" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
@@ -2728,7 +2752,7 @@
     <row r="1" spans="1:35" x14ac:dyDescent="0.3">
       <c r="M1" s="3">
         <f t="shared" ref="M1:V1" si="0">SUBTOTAL(9,M3:M475)</f>
-        <v>2708562.5998849981</v>
+        <v>2659254.559884998</v>
       </c>
       <c r="N1" s="3">
         <f t="shared" si="0"/>
@@ -2740,7 +2764,7 @@
       </c>
       <c r="P1" s="3">
         <f t="shared" si="0"/>
-        <v>284892.7100000002</v>
+        <v>235584.67</v>
       </c>
       <c r="Q1" s="3">
         <f t="shared" si="0"/>
@@ -2766,14 +2790,14 @@
         <f t="shared" si="0"/>
         <v>48800</v>
       </c>
-      <c r="Y1" s="6">
+      <c r="Y1" s="3">
         <f>SUBTOTAL(9,Y3:Y475)</f>
         <v>1098400</v>
       </c>
-      <c r="Z1" s="5"/>
+      <c r="Z1" s="7"/>
       <c r="AE1" s="3">
         <f>SUBTOTAL(9,AE3:AE475)</f>
-        <v>2967374.5998849971</v>
+        <v>2918066.5598849971</v>
       </c>
       <c r="AF1" s="3">
         <f>SUBTOTAL(9,AF3:AF475)</f>
@@ -2781,7 +2805,7 @@
       </c>
       <c r="AG1" s="3">
         <f>SUBTOTAL(9,AG3:AG475)</f>
-        <v>4146861.6098849988</v>
+        <v>4097553.5698849978</v>
       </c>
     </row>
     <row r="2" spans="1:35" x14ac:dyDescent="0.3">
@@ -3197,7 +3221,7 @@
       </c>
       <c r="M6" s="4">
         <f t="shared" si="3"/>
-        <v>6726.74</v>
+        <v>6015.38</v>
       </c>
       <c r="N6" s="4">
         <v>2801.97</v>
@@ -3206,7 +3230,7 @@
         <v>1355.69</v>
       </c>
       <c r="P6" s="4">
-        <v>2156.66</v>
+        <v>1445.3</v>
       </c>
       <c r="Q6" s="4">
         <v>412.42</v>
@@ -3237,7 +3261,7 @@
       </c>
       <c r="AE6" s="4">
         <f t="shared" si="4"/>
-        <v>7638.74</v>
+        <v>6927.38</v>
       </c>
       <c r="AF6">
         <f t="shared" si="1"/>
@@ -3245,7 +3269,7 @@
       </c>
       <c r="AG6" s="4">
         <f t="shared" si="2"/>
-        <v>7638.74</v>
+        <v>6927.38</v>
       </c>
       <c r="AI6" t="s">
         <v>47</v>
@@ -3267,7 +3291,7 @@
       <c r="E7">
         <v>5</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="8" t="s">
         <v>366</v>
       </c>
       <c r="G7" t="s">
@@ -3319,7 +3343,7 @@
       <c r="X7" t="s">
         <v>36</v>
       </c>
-      <c r="Y7">
+      <c r="Y7" s="8">
         <v>3500</v>
       </c>
       <c r="AC7" t="s">
@@ -3380,7 +3404,7 @@
       </c>
       <c r="M8" s="4">
         <f t="shared" si="3"/>
-        <v>6122.2300000000005</v>
+        <v>5517.39</v>
       </c>
       <c r="N8" s="4">
         <v>2801.97</v>
@@ -3389,7 +3413,7 @@
         <v>1552.95</v>
       </c>
       <c r="P8" s="4">
-        <v>1372.59</v>
+        <v>767.75</v>
       </c>
       <c r="Q8" s="4">
         <v>394.72</v>
@@ -3420,7 +3444,7 @@
       </c>
       <c r="AE8" s="4">
         <f t="shared" si="4"/>
-        <v>7110.2300000000005</v>
+        <v>6505.39</v>
       </c>
       <c r="AF8">
         <f t="shared" si="1"/>
@@ -3428,7 +3452,7 @@
       </c>
       <c r="AG8" s="4">
         <f t="shared" si="2"/>
-        <v>7110.2300000000005</v>
+        <v>6505.39</v>
       </c>
       <c r="AI8" t="s">
         <v>47</v>
@@ -3740,7 +3764,7 @@
       </c>
       <c r="M12" s="4">
         <f t="shared" si="3"/>
-        <v>4747.9799999999996</v>
+        <v>4227.26</v>
       </c>
       <c r="N12" s="4">
         <v>2801.97</v>
@@ -3749,7 +3773,7 @@
         <v>90.3</v>
       </c>
       <c r="P12" s="4">
-        <v>1597.72</v>
+        <v>1077</v>
       </c>
       <c r="Q12" s="4">
         <v>257.99</v>
@@ -3780,7 +3804,7 @@
       </c>
       <c r="AE12" s="4">
         <f t="shared" si="4"/>
-        <v>5621.98</v>
+        <v>5101.26</v>
       </c>
       <c r="AF12">
         <f t="shared" si="1"/>
@@ -3788,7 +3812,7 @@
       </c>
       <c r="AG12" s="4">
         <f t="shared" si="2"/>
-        <v>5621.98</v>
+        <v>5101.26</v>
       </c>
       <c r="AI12" t="s">
         <v>39</v>
@@ -4010,7 +4034,7 @@
       </c>
       <c r="M15" s="4">
         <f t="shared" si="3"/>
-        <v>6776.5599999999995</v>
+        <v>6041.2</v>
       </c>
       <c r="N15" s="4">
         <v>2801.97</v>
@@ -4019,7 +4043,7 @@
         <v>1356.23</v>
       </c>
       <c r="P15" s="4">
-        <v>2205.8599999999997</v>
+        <v>1470.5</v>
       </c>
       <c r="Q15" s="4">
         <v>412.5</v>
@@ -4050,7 +4074,7 @@
       </c>
       <c r="AE15" s="4">
         <f t="shared" si="4"/>
-        <v>6776.5599999999995</v>
+        <v>6041.2</v>
       </c>
       <c r="AF15">
         <f t="shared" si="1"/>
@@ -4058,7 +4082,7 @@
       </c>
       <c r="AG15" s="4">
         <f t="shared" si="2"/>
-        <v>6776.5599999999995</v>
+        <v>6041.2</v>
       </c>
       <c r="AI15" t="s">
         <v>47</v>
@@ -4280,7 +4304,7 @@
       </c>
       <c r="M18" s="4">
         <f t="shared" si="3"/>
-        <v>7614.7799999999988</v>
+        <v>6860.2199999999993</v>
       </c>
       <c r="N18" s="4">
         <v>2801.97</v>
@@ -4289,7 +4313,7 @@
         <v>2149.92</v>
       </c>
       <c r="P18" s="4">
-        <v>2144.48</v>
+        <v>1389.92</v>
       </c>
       <c r="Q18" s="4">
         <v>518.41</v>
@@ -4320,7 +4344,7 @@
       </c>
       <c r="AE18" s="4">
         <f t="shared" si="4"/>
-        <v>8526.7799999999988</v>
+        <v>7772.2199999999993</v>
       </c>
       <c r="AF18">
         <f t="shared" si="1"/>
@@ -4328,7 +4352,7 @@
       </c>
       <c r="AG18" s="4">
         <f t="shared" si="2"/>
-        <v>8526.7799999999988</v>
+        <v>7772.2199999999993</v>
       </c>
       <c r="AI18" t="s">
         <v>47</v>
@@ -5985,7 +6009,7 @@
       <c r="E37">
         <v>35</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F37" s="8" t="s">
         <v>310</v>
       </c>
       <c r="G37" t="s">
@@ -6037,7 +6061,7 @@
       <c r="X37" t="s">
         <v>36</v>
       </c>
-      <c r="Y37">
+      <c r="Y37" s="8">
         <f>18000+13000</f>
         <v>31000</v>
       </c>
@@ -6279,7 +6303,7 @@
       </c>
       <c r="M40" s="4">
         <f t="shared" si="3"/>
-        <v>5963.3099999999995</v>
+        <v>5674.67</v>
       </c>
       <c r="N40" s="4">
         <v>2801.97</v>
@@ -6288,7 +6312,7 @@
         <v>1300.0300000000002</v>
       </c>
       <c r="P40" s="4">
-        <v>1458.04</v>
+        <v>1169.4000000000001</v>
       </c>
       <c r="Q40" s="4">
         <v>403.27</v>
@@ -6319,7 +6343,7 @@
       </c>
       <c r="AE40" s="4">
         <f t="shared" si="4"/>
-        <v>6723.3099999999995</v>
+        <v>6434.67</v>
       </c>
       <c r="AF40">
         <f t="shared" si="1"/>
@@ -6327,7 +6351,7 @@
       </c>
       <c r="AG40" s="4">
         <f t="shared" si="2"/>
-        <v>6723.3099999999995</v>
+        <v>6434.67</v>
       </c>
       <c r="AI40" t="s">
         <v>47</v>
@@ -6709,7 +6733,7 @@
       <c r="E45">
         <v>43</v>
       </c>
-      <c r="F45" t="s">
+      <c r="F45" s="8" t="s">
         <v>263</v>
       </c>
       <c r="G45" t="s">
@@ -6761,7 +6785,7 @@
       <c r="X45" t="s">
         <v>36</v>
       </c>
-      <c r="Y45">
+      <c r="Y45" s="8">
         <v>15000</v>
       </c>
       <c r="AC45" t="s">
@@ -7702,7 +7726,7 @@
       <c r="E56">
         <v>54</v>
       </c>
-      <c r="F56" t="s">
+      <c r="F56" s="9" t="s">
         <v>342</v>
       </c>
       <c r="G56" t="s">
@@ -7722,7 +7746,7 @@
       </c>
       <c r="M56" s="4">
         <f t="shared" si="3"/>
-        <v>6152.6900000000005</v>
+        <v>5688.5300000000007</v>
       </c>
       <c r="N56" s="4">
         <v>3356.8</v>
@@ -7731,7 +7755,7 @@
         <v>1132.3699999999999</v>
       </c>
       <c r="P56" s="4">
-        <v>1264.8</v>
+        <v>800.64</v>
       </c>
       <c r="Q56" s="4">
         <v>398.72</v>
@@ -7754,7 +7778,7 @@
       <c r="X56" t="s">
         <v>36</v>
       </c>
-      <c r="Y56">
+      <c r="Y56" s="8">
         <v>4500</v>
       </c>
       <c r="AC56" t="s">
@@ -7765,7 +7789,7 @@
       </c>
       <c r="AE56" s="4">
         <f t="shared" si="4"/>
-        <v>7064.6900000000005</v>
+        <v>6600.5300000000007</v>
       </c>
       <c r="AF56">
         <f t="shared" si="1"/>
@@ -7773,7 +7797,7 @@
       </c>
       <c r="AG56" s="4">
         <f t="shared" si="2"/>
-        <v>11564.69</v>
+        <v>11100.53</v>
       </c>
       <c r="AI56" t="s">
         <v>47</v>
@@ -8538,7 +8562,7 @@
       </c>
       <c r="M65" s="4">
         <f t="shared" si="3"/>
-        <v>13869.689999999999</v>
+        <v>13441.689999999999</v>
       </c>
       <c r="N65" s="4">
         <v>5783.25</v>
@@ -8547,7 +8571,7 @@
         <v>3230.57</v>
       </c>
       <c r="P65" s="4">
-        <v>2867.35</v>
+        <v>2439.35</v>
       </c>
       <c r="Q65" s="4">
         <v>1988.52</v>
@@ -8578,7 +8602,7 @@
       </c>
       <c r="AE65" s="4">
         <f t="shared" si="4"/>
-        <v>14819.689999999999</v>
+        <v>14391.689999999999</v>
       </c>
       <c r="AF65">
         <f t="shared" si="1"/>
@@ -8586,7 +8610,7 @@
       </c>
       <c r="AG65" s="4">
         <f t="shared" si="2"/>
-        <v>14819.689999999999</v>
+        <v>14391.689999999999</v>
       </c>
       <c r="AI65" t="s">
         <v>39</v>
@@ -8625,7 +8649,7 @@
       </c>
       <c r="M66" s="4">
         <f t="shared" si="3"/>
-        <v>6635.58</v>
+        <v>6300.9400000000005</v>
       </c>
       <c r="N66" s="4">
         <v>3195.53</v>
@@ -8634,7 +8658,7 @@
         <v>1854.73</v>
       </c>
       <c r="P66" s="4">
-        <v>1109.28</v>
+        <v>774.64</v>
       </c>
       <c r="Q66" s="4">
         <v>476.04</v>
@@ -8665,7 +8689,7 @@
       </c>
       <c r="AE66" s="4">
         <f t="shared" si="4"/>
-        <v>7623.58</v>
+        <v>7288.9400000000005</v>
       </c>
       <c r="AF66">
         <f t="shared" si="1"/>
@@ -8673,7 +8697,7 @@
       </c>
       <c r="AG66" s="4">
         <f t="shared" si="2"/>
-        <v>7623.58</v>
+        <v>7288.9400000000005</v>
       </c>
       <c r="AI66" t="s">
         <v>39</v>
@@ -8785,7 +8809,7 @@
       <c r="E68">
         <v>66</v>
       </c>
-      <c r="F68" t="s">
+      <c r="F68" s="9" t="s">
         <v>573</v>
       </c>
       <c r="G68" t="s">
@@ -8805,7 +8829,7 @@
       </c>
       <c r="M68" s="4">
         <f t="shared" ref="M68:M131" si="7">N68+O68+P68+Q68-S68+R68</f>
-        <v>5789.55</v>
+        <v>5532.8600000000006</v>
       </c>
       <c r="N68" s="4">
         <v>3356.8</v>
@@ -8814,7 +8838,7 @@
         <v>1376.29</v>
       </c>
       <c r="P68" s="4">
-        <v>615.32999999999993</v>
+        <v>358.64</v>
       </c>
       <c r="Q68" s="4">
         <v>441.13</v>
@@ -8837,7 +8861,7 @@
       <c r="X68" t="s">
         <v>36</v>
       </c>
-      <c r="Y68">
+      <c r="Y68" s="8">
         <v>5000</v>
       </c>
       <c r="AC68" t="s">
@@ -8848,7 +8872,7 @@
       </c>
       <c r="AE68" s="4">
         <f t="shared" ref="AE68:AE131" si="8">M68+T68+V68</f>
-        <v>6739.55</v>
+        <v>6482.8600000000006</v>
       </c>
       <c r="AF68">
         <f t="shared" si="5"/>
@@ -8856,7 +8880,7 @@
       </c>
       <c r="AG68" s="4">
         <f t="shared" si="6"/>
-        <v>11739.55</v>
+        <v>11482.86</v>
       </c>
       <c r="AI68" t="s">
         <v>47</v>
@@ -9058,7 +9082,7 @@
       <c r="E71">
         <v>70</v>
       </c>
-      <c r="F71" t="s">
+      <c r="F71" s="8" t="s">
         <v>652</v>
       </c>
       <c r="G71" t="s">
@@ -9078,7 +9102,7 @@
       </c>
       <c r="M71" s="4">
         <f t="shared" si="7"/>
-        <v>9097.9900000000016</v>
+        <v>9075.35</v>
       </c>
       <c r="N71" s="4">
         <v>3356.8</v>
@@ -9087,7 +9111,7 @@
         <v>2832.6800000000003</v>
       </c>
       <c r="P71" s="4">
-        <v>1869.06</v>
+        <v>1846.42</v>
       </c>
       <c r="Q71" s="4">
         <v>1039.4499999999998</v>
@@ -9110,7 +9134,7 @@
       <c r="X71" t="s">
         <v>36</v>
       </c>
-      <c r="Y71">
+      <c r="Y71" s="8">
         <v>15000</v>
       </c>
       <c r="AC71" t="s">
@@ -9121,7 +9145,7 @@
       </c>
       <c r="AE71" s="4">
         <f t="shared" si="8"/>
-        <v>10047.990000000002</v>
+        <v>10025.35</v>
       </c>
       <c r="AF71">
         <f t="shared" si="5"/>
@@ -9129,7 +9153,7 @@
       </c>
       <c r="AG71" s="4">
         <f t="shared" si="6"/>
-        <v>25047.99</v>
+        <v>25025.35</v>
       </c>
       <c r="AI71" t="s">
         <v>47</v>
@@ -9261,7 +9285,7 @@
       </c>
       <c r="M73" s="4">
         <f t="shared" si="7"/>
-        <v>5466.16</v>
+        <v>4900.16</v>
       </c>
       <c r="N73" s="4">
         <v>2302.75</v>
@@ -9270,7 +9294,7 @@
         <v>1388.51</v>
       </c>
       <c r="P73" s="4">
-        <v>1418</v>
+        <v>852</v>
       </c>
       <c r="Q73" s="4">
         <v>356.9</v>
@@ -9301,7 +9325,7 @@
       </c>
       <c r="AE73" s="4">
         <f t="shared" si="8"/>
-        <v>6416.16</v>
+        <v>5850.16</v>
       </c>
       <c r="AF73">
         <f t="shared" si="5"/>
@@ -9309,7 +9333,7 @@
       </c>
       <c r="AG73" s="4">
         <f t="shared" si="6"/>
-        <v>6416.16</v>
+        <v>5850.16</v>
       </c>
       <c r="AI73" t="s">
         <v>47</v>
@@ -9621,7 +9645,7 @@
       </c>
       <c r="M77" s="4">
         <f t="shared" si="7"/>
-        <v>13766.060000000001</v>
+        <v>13408.420000000002</v>
       </c>
       <c r="N77" s="4">
         <v>5377.9</v>
@@ -9630,7 +9654,7 @@
         <v>4972.5700000000006</v>
       </c>
       <c r="P77" s="4">
-        <v>1229.08</v>
+        <v>871.44</v>
       </c>
       <c r="Q77" s="4">
         <v>2186.5100000000002</v>
@@ -9661,7 +9685,7 @@
       </c>
       <c r="AE77" s="4">
         <f t="shared" si="8"/>
-        <v>14754.060000000001</v>
+        <v>14396.420000000002</v>
       </c>
       <c r="AF77">
         <f t="shared" si="5"/>
@@ -9669,7 +9693,7 @@
       </c>
       <c r="AG77" s="4">
         <f t="shared" si="6"/>
-        <v>14754.060000000001</v>
+        <v>14396.420000000002</v>
       </c>
       <c r="AI77" t="s">
         <v>47</v>
@@ -9781,7 +9805,7 @@
       <c r="E79">
         <v>78</v>
       </c>
-      <c r="F79" t="s">
+      <c r="F79" s="8" t="s">
         <v>528</v>
       </c>
       <c r="G79" t="s">
@@ -9833,7 +9857,7 @@
       <c r="X79" t="s">
         <v>36</v>
       </c>
-      <c r="Y79">
+      <c r="Y79" s="8">
         <v>15000</v>
       </c>
       <c r="AC79" t="s">
@@ -10164,7 +10188,7 @@
       </c>
       <c r="M83" s="4">
         <f t="shared" si="7"/>
-        <v>12469.699999999999</v>
+        <v>11989.3</v>
       </c>
       <c r="N83" s="4">
         <v>5377.9</v>
@@ -10173,7 +10197,7 @@
         <v>4039.83</v>
       </c>
       <c r="P83" s="4">
-        <v>1228.8899999999999</v>
+        <v>748.49</v>
       </c>
       <c r="Q83" s="4">
         <v>1823.08</v>
@@ -10204,7 +10228,7 @@
       </c>
       <c r="AE83" s="4">
         <f t="shared" si="8"/>
-        <v>13533.699999999999</v>
+        <v>13053.3</v>
       </c>
       <c r="AF83">
         <f t="shared" si="5"/>
@@ -10212,7 +10236,7 @@
       </c>
       <c r="AG83" s="4">
         <f t="shared" si="6"/>
-        <v>13533.699999999999</v>
+        <v>13053.3</v>
       </c>
       <c r="AI83" t="s">
         <v>47</v>
@@ -10254,7 +10278,7 @@
       </c>
       <c r="M84" s="4">
         <f t="shared" si="7"/>
-        <v>6704.46</v>
+        <v>6429.82</v>
       </c>
       <c r="N84" s="4">
         <v>2801.97</v>
@@ -10263,7 +10287,7 @@
         <v>1905.83</v>
       </c>
       <c r="P84" s="4">
-        <v>1511.85</v>
+        <v>1237.21</v>
       </c>
       <c r="Q84" s="4">
         <v>484.81</v>
@@ -10294,7 +10318,7 @@
       </c>
       <c r="AE84" s="4">
         <f t="shared" si="8"/>
-        <v>7578.46</v>
+        <v>7303.82</v>
       </c>
       <c r="AF84">
         <f t="shared" si="5"/>
@@ -10302,7 +10326,7 @@
       </c>
       <c r="AG84" s="4">
         <f t="shared" si="6"/>
-        <v>7578.46</v>
+        <v>7303.82</v>
       </c>
       <c r="AI84" t="s">
         <v>47</v>
@@ -10777,7 +10801,7 @@
       <c r="E90">
         <v>89</v>
       </c>
-      <c r="F90" t="s">
+      <c r="F90" s="8" t="s">
         <v>543</v>
       </c>
       <c r="G90" t="s">
@@ -10797,7 +10821,7 @@
       </c>
       <c r="M90" s="4">
         <f t="shared" si="7"/>
-        <v>6321.0300000000007</v>
+        <v>6298.3899999999994</v>
       </c>
       <c r="N90" s="4">
         <v>3356.8</v>
@@ -10806,7 +10830,7 @@
         <v>1779.9099999999999</v>
       </c>
       <c r="P90" s="4">
-        <v>724.82999999999993</v>
+        <v>702.19</v>
       </c>
       <c r="Q90" s="4">
         <v>459.49</v>
@@ -10829,7 +10853,7 @@
       <c r="X90" t="s">
         <v>36</v>
       </c>
-      <c r="Y90">
+      <c r="Y90" s="8">
         <v>15000</v>
       </c>
       <c r="AC90" t="s">
@@ -10840,7 +10864,7 @@
       </c>
       <c r="AE90" s="4">
         <f t="shared" si="8"/>
-        <v>7195.0300000000007</v>
+        <v>7172.3899999999994</v>
       </c>
       <c r="AF90">
         <f t="shared" si="5"/>
@@ -10848,7 +10872,7 @@
       </c>
       <c r="AG90" s="4">
         <f t="shared" si="6"/>
-        <v>22195.03</v>
+        <v>22172.39</v>
       </c>
       <c r="AI90" t="s">
         <v>47</v>
@@ -10980,7 +11004,7 @@
       </c>
       <c r="M92" s="4">
         <f t="shared" si="7"/>
-        <v>5943.0599999999995</v>
+        <v>5436.93</v>
       </c>
       <c r="N92" s="4">
         <v>3364.8</v>
@@ -10989,7 +11013,7 @@
         <v>1095.32</v>
       </c>
       <c r="P92" s="4">
-        <v>1082.8499999999999</v>
+        <v>576.72</v>
       </c>
       <c r="Q92" s="4">
         <v>400.09</v>
@@ -11020,7 +11044,7 @@
       </c>
       <c r="AE92" s="4">
         <f t="shared" si="8"/>
-        <v>6893.0599999999995</v>
+        <v>6386.93</v>
       </c>
       <c r="AF92">
         <f t="shared" si="5"/>
@@ -11028,7 +11052,7 @@
       </c>
       <c r="AG92" s="4">
         <f t="shared" si="6"/>
-        <v>6893.0599999999995</v>
+        <v>6386.93</v>
       </c>
       <c r="AI92" t="s">
         <v>47</v>
@@ -11767,7 +11791,7 @@
       <c r="E101">
         <v>100</v>
       </c>
-      <c r="F101" t="s">
+      <c r="F101" s="8" t="s">
         <v>530</v>
       </c>
       <c r="G101" t="s">
@@ -11819,7 +11843,7 @@
       <c r="X101" t="s">
         <v>36</v>
       </c>
-      <c r="Y101">
+      <c r="Y101" s="8">
         <v>14000</v>
       </c>
       <c r="AC101" t="s">
@@ -11860,7 +11884,7 @@
       <c r="E102">
         <v>101</v>
       </c>
-      <c r="F102" t="s">
+      <c r="F102" s="8" t="s">
         <v>535</v>
       </c>
       <c r="G102" t="s">
@@ -11880,7 +11904,7 @@
       </c>
       <c r="M102" s="4">
         <f t="shared" si="7"/>
-        <v>8877.5400000000009</v>
+        <v>8829.74</v>
       </c>
       <c r="N102" s="4">
         <v>4681.28</v>
@@ -11889,7 +11913,7 @@
         <v>2551.09</v>
       </c>
       <c r="P102" s="4">
-        <v>694.6400000000001</v>
+        <v>646.84</v>
       </c>
       <c r="Q102" s="4">
         <v>950.53</v>
@@ -11912,7 +11936,7 @@
       <c r="X102" t="s">
         <v>36</v>
       </c>
-      <c r="Y102">
+      <c r="Y102" s="8">
         <v>14000</v>
       </c>
       <c r="AC102" t="s">
@@ -11923,7 +11947,7 @@
       </c>
       <c r="AE102" s="4">
         <f t="shared" si="8"/>
-        <v>9827.5400000000009</v>
+        <v>9779.74</v>
       </c>
       <c r="AF102">
         <f t="shared" si="5"/>
@@ -11931,7 +11955,7 @@
       </c>
       <c r="AG102" s="4">
         <f t="shared" si="6"/>
-        <v>23827.54</v>
+        <v>23779.739999999998</v>
       </c>
       <c r="AI102" t="s">
         <v>47</v>
@@ -12043,7 +12067,7 @@
       <c r="E104">
         <v>104</v>
       </c>
-      <c r="F104" t="s">
+      <c r="F104" s="8" t="s">
         <v>50</v>
       </c>
       <c r="G104" t="s">
@@ -12095,7 +12119,7 @@
       <c r="X104" t="s">
         <v>36</v>
       </c>
-      <c r="Y104">
+      <c r="Y104" s="8">
         <v>14000</v>
       </c>
       <c r="AC104" t="s">
@@ -12856,7 +12880,7 @@
       <c r="E113">
         <v>113</v>
       </c>
-      <c r="F113" t="s">
+      <c r="F113" s="8" t="s">
         <v>156</v>
       </c>
       <c r="G113" t="s">
@@ -12876,7 +12900,7 @@
       </c>
       <c r="M113" s="4">
         <f t="shared" si="7"/>
-        <v>6736.86</v>
+        <v>6714.22</v>
       </c>
       <c r="N113" s="4">
         <v>3356.8</v>
@@ -12885,7 +12909,7 @@
         <v>2440.12</v>
       </c>
       <c r="P113" s="4">
-        <v>349.30999999999995</v>
+        <v>326.66999999999996</v>
       </c>
       <c r="Q113" s="4">
         <v>590.63</v>
@@ -12908,7 +12932,7 @@
       <c r="X113" t="s">
         <v>36</v>
       </c>
-      <c r="Y113">
+      <c r="Y113" s="8">
         <v>13000</v>
       </c>
       <c r="AC113" t="s">
@@ -12919,7 +12943,7 @@
       </c>
       <c r="AE113" s="4">
         <f t="shared" si="8"/>
-        <v>7762.86</v>
+        <v>7740.22</v>
       </c>
       <c r="AF113">
         <f t="shared" si="5"/>
@@ -12927,7 +12951,7 @@
       </c>
       <c r="AG113" s="4">
         <f t="shared" si="6"/>
-        <v>20762.86</v>
+        <v>20740.22</v>
       </c>
       <c r="AI113" t="s">
         <v>47</v>
@@ -13059,7 +13083,7 @@
       </c>
       <c r="M115" s="4">
         <f t="shared" si="7"/>
-        <v>6276.6799999999985</v>
+        <v>6254.0399999999991</v>
       </c>
       <c r="N115" s="4">
         <v>2302.75</v>
@@ -13068,7 +13092,7 @@
         <v>2376.73</v>
       </c>
       <c r="P115" s="4">
-        <v>1129.6300000000001</v>
+        <v>1106.99</v>
       </c>
       <c r="Q115" s="4">
         <v>467.57</v>
@@ -13099,7 +13123,7 @@
       </c>
       <c r="AE115" s="4">
         <f t="shared" si="8"/>
-        <v>7188.6799999999985</v>
+        <v>7166.0399999999991</v>
       </c>
       <c r="AF115">
         <f t="shared" si="5"/>
@@ -13107,7 +13131,7 @@
       </c>
       <c r="AG115" s="4">
         <f t="shared" si="6"/>
-        <v>7188.6799999999985</v>
+        <v>7166.0399999999991</v>
       </c>
       <c r="AI115" t="s">
         <v>47</v>
@@ -13779,7 +13803,7 @@
       </c>
       <c r="M123" s="4">
         <f t="shared" si="7"/>
-        <v>4424.6500000000005</v>
+        <v>4085.0499999999997</v>
       </c>
       <c r="N123" s="4">
         <v>2302.75</v>
@@ -13788,7 +13812,7 @@
         <v>907.38</v>
       </c>
       <c r="P123" s="4">
-        <v>915.33999999999992</v>
+        <v>575.74</v>
       </c>
       <c r="Q123" s="4">
         <v>299.18</v>
@@ -13819,7 +13843,7 @@
       </c>
       <c r="AE123" s="4">
         <f t="shared" si="8"/>
-        <v>4994.6500000000005</v>
+        <v>4655.0499999999993</v>
       </c>
       <c r="AF123">
         <f t="shared" si="5"/>
@@ -13827,7 +13851,7 @@
       </c>
       <c r="AG123" s="4">
         <f t="shared" si="6"/>
-        <v>4994.6500000000005</v>
+        <v>4655.0499999999993</v>
       </c>
       <c r="AI123" t="s">
         <v>47</v>
@@ -13869,7 +13893,7 @@
       </c>
       <c r="M124" s="4">
         <f t="shared" si="7"/>
-        <v>5095.95</v>
+        <v>4825.83</v>
       </c>
       <c r="N124" s="4">
         <v>2302.75</v>
@@ -13878,7 +13902,7 @@
         <v>1451.54</v>
       </c>
       <c r="P124" s="4">
-        <v>976.75</v>
+        <v>706.63</v>
       </c>
       <c r="Q124" s="4">
         <v>364.91</v>
@@ -13909,7 +13933,7 @@
       </c>
       <c r="AE124" s="4">
         <f t="shared" si="8"/>
-        <v>5969.95</v>
+        <v>5699.83</v>
       </c>
       <c r="AF124">
         <f t="shared" si="5"/>
@@ -13917,7 +13941,7 @@
       </c>
       <c r="AG124" s="4">
         <f t="shared" si="6"/>
-        <v>5969.95</v>
+        <v>5699.83</v>
       </c>
       <c r="AI124" t="s">
         <v>47</v>
@@ -13939,7 +13963,7 @@
       <c r="E125">
         <v>126</v>
       </c>
-      <c r="F125" t="s">
+      <c r="F125" s="8" t="s">
         <v>642</v>
       </c>
       <c r="G125" t="s">
@@ -13991,7 +14015,7 @@
       <c r="X125" t="s">
         <v>36</v>
       </c>
-      <c r="Y125">
+      <c r="Y125" s="8">
         <v>15000</v>
       </c>
       <c r="AC125" t="s">
@@ -14502,7 +14526,7 @@
       </c>
       <c r="M131" s="4">
         <f t="shared" si="7"/>
-        <v>9186.68</v>
+        <v>8620.68</v>
       </c>
       <c r="N131" s="4">
         <v>3356.8</v>
@@ -14511,7 +14535,7 @@
         <v>3744.08</v>
       </c>
       <c r="P131" s="4">
-        <v>1019.02</v>
+        <v>453.02</v>
       </c>
       <c r="Q131" s="4">
         <v>1066.78</v>
@@ -14534,7 +14558,7 @@
       <c r="X131" t="s">
         <v>36</v>
       </c>
-      <c r="Y131">
+      <c r="Y131" s="8">
         <v>10000</v>
       </c>
       <c r="AC131" t="s">
@@ -14545,7 +14569,7 @@
       </c>
       <c r="AE131" s="4">
         <f t="shared" si="8"/>
-        <v>10136.68</v>
+        <v>9570.68</v>
       </c>
       <c r="AF131">
         <f t="shared" ref="AF131:AF194" si="9">U131+Y131</f>
@@ -14553,7 +14577,7 @@
       </c>
       <c r="AG131" s="4">
         <f t="shared" ref="AG131:AG194" si="10">AF131+AE131</f>
-        <v>20136.68</v>
+        <v>19570.68</v>
       </c>
       <c r="AI131" t="s">
         <v>47</v>
@@ -14938,7 +14962,7 @@
       <c r="E136">
         <v>137</v>
       </c>
-      <c r="F136" t="s">
+      <c r="F136" s="8" t="s">
         <v>653</v>
       </c>
       <c r="G136" t="s">
@@ -14958,7 +14982,7 @@
       </c>
       <c r="M136" s="4">
         <f t="shared" si="11"/>
-        <v>10601.24</v>
+        <v>10188.34</v>
       </c>
       <c r="N136" s="4">
         <v>4681.28</v>
@@ -14967,7 +14991,7 @@
         <v>3392.2900000000004</v>
       </c>
       <c r="P136" s="4">
-        <v>1102.92</v>
+        <v>690.02</v>
       </c>
       <c r="Q136" s="4">
         <v>1424.75</v>
@@ -14990,7 +15014,7 @@
       <c r="X136" t="s">
         <v>36</v>
       </c>
-      <c r="Y136">
+      <c r="Y136" s="8">
         <v>14000</v>
       </c>
       <c r="AC136" t="s">
@@ -15001,7 +15025,7 @@
       </c>
       <c r="AE136" s="4">
         <f t="shared" si="12"/>
-        <v>11475.24</v>
+        <v>11062.34</v>
       </c>
       <c r="AF136">
         <f t="shared" si="9"/>
@@ -15009,7 +15033,7 @@
       </c>
       <c r="AG136" s="4">
         <f t="shared" si="10"/>
-        <v>25475.239999999998</v>
+        <v>25062.34</v>
       </c>
       <c r="AI136" t="s">
         <v>47</v>
@@ -15234,7 +15258,7 @@
       </c>
       <c r="M139" s="4">
         <f t="shared" si="11"/>
-        <v>7451.42</v>
+        <v>6959.42</v>
       </c>
       <c r="N139" s="4">
         <v>2801.97</v>
@@ -15243,7 +15267,7 @@
         <v>2437.5299999999997</v>
       </c>
       <c r="P139" s="4">
-        <v>1649.63</v>
+        <v>1157.6300000000001</v>
       </c>
       <c r="Q139" s="4">
         <v>562.29</v>
@@ -15274,7 +15298,7 @@
       </c>
       <c r="AE139" s="4">
         <f t="shared" si="12"/>
-        <v>8363.42</v>
+        <v>7871.42</v>
       </c>
       <c r="AF139">
         <f t="shared" si="9"/>
@@ -15282,7 +15306,7 @@
       </c>
       <c r="AG139" s="4">
         <f t="shared" si="10"/>
-        <v>8363.42</v>
+        <v>7871.42</v>
       </c>
       <c r="AI139" t="s">
         <v>47</v>
@@ -15324,7 +15348,7 @@
       </c>
       <c r="M140" s="4">
         <f t="shared" si="11"/>
-        <v>4648.2800000000007</v>
+        <v>4291.6400000000003</v>
       </c>
       <c r="N140" s="4">
         <v>2801.97</v>
@@ -15333,7 +15357,7 @@
         <v>509.38</v>
       </c>
       <c r="P140" s="4">
-        <v>1084.8400000000001</v>
+        <v>728.2</v>
       </c>
       <c r="Q140" s="4">
         <v>252.09</v>
@@ -15364,7 +15388,7 @@
       </c>
       <c r="AE140" s="4">
         <f t="shared" si="12"/>
-        <v>5446.2800000000007</v>
+        <v>5089.6400000000003</v>
       </c>
       <c r="AF140">
         <f t="shared" si="9"/>
@@ -15372,7 +15396,7 @@
       </c>
       <c r="AG140" s="4">
         <f t="shared" si="10"/>
-        <v>5446.2800000000007</v>
+        <v>5089.6400000000003</v>
       </c>
       <c r="AI140" t="s">
         <v>47</v>
@@ -15774,7 +15798,7 @@
       </c>
       <c r="M145" s="4">
         <f t="shared" si="11"/>
-        <v>7598.9699999999993</v>
+        <v>7576.33</v>
       </c>
       <c r="N145" s="4">
         <v>2801.97</v>
@@ -15783,7 +15807,7 @@
         <v>3294.42</v>
       </c>
       <c r="P145" s="4">
-        <v>713.53</v>
+        <v>690.89</v>
       </c>
       <c r="Q145" s="4">
         <v>789.05</v>
@@ -15814,7 +15838,7 @@
       </c>
       <c r="AE145" s="4">
         <f t="shared" si="12"/>
-        <v>8510.9699999999993</v>
+        <v>8488.33</v>
       </c>
       <c r="AF145">
         <f t="shared" si="9"/>
@@ -15822,7 +15846,7 @@
       </c>
       <c r="AG145" s="4">
         <f t="shared" si="10"/>
-        <v>8510.9699999999993</v>
+        <v>8488.33</v>
       </c>
       <c r="AI145" t="s">
         <v>47</v>
@@ -15844,7 +15868,7 @@
       <c r="E146">
         <v>147</v>
       </c>
-      <c r="F146" t="s">
+      <c r="F146" s="8" t="s">
         <v>427</v>
       </c>
       <c r="G146" t="s">
@@ -15864,7 +15888,7 @@
       </c>
       <c r="M146" s="4">
         <f t="shared" si="11"/>
-        <v>8084.3799999999992</v>
+        <v>7355.26</v>
       </c>
       <c r="N146" s="4">
         <v>3356.8</v>
@@ -15873,7 +15897,7 @@
         <v>2977.26</v>
       </c>
       <c r="P146" s="4">
-        <v>1029.1199999999999</v>
+        <v>300</v>
       </c>
       <c r="Q146" s="4">
         <v>721.2</v>
@@ -15896,7 +15920,7 @@
       <c r="X146" t="s">
         <v>36</v>
       </c>
-      <c r="Y146">
+      <c r="Y146" s="8">
         <v>12000</v>
       </c>
       <c r="AC146" t="s">
@@ -15907,7 +15931,7 @@
       </c>
       <c r="AE146" s="4">
         <f t="shared" si="12"/>
-        <v>9148.3799999999992</v>
+        <v>8419.26</v>
       </c>
       <c r="AF146">
         <f t="shared" si="9"/>
@@ -15915,7 +15939,7 @@
       </c>
       <c r="AG146" s="4">
         <f t="shared" si="10"/>
-        <v>21148.379999999997</v>
+        <v>20419.260000000002</v>
       </c>
       <c r="AI146" t="s">
         <v>47</v>
@@ -16233,7 +16257,7 @@
       </c>
       <c r="M150" s="4">
         <f t="shared" si="11"/>
-        <v>3890.24</v>
+        <v>3554.24</v>
       </c>
       <c r="N150" s="4">
         <v>2302.75</v>
@@ -16242,7 +16266,7 @@
         <v>264.88</v>
       </c>
       <c r="P150" s="4">
-        <v>1098.2</v>
+        <v>762.2</v>
       </c>
       <c r="Q150" s="4">
         <v>224.41</v>
@@ -16273,7 +16297,7 @@
       </c>
       <c r="AE150" s="4">
         <f t="shared" si="12"/>
-        <v>4764.24</v>
+        <v>4428.24</v>
       </c>
       <c r="AF150">
         <f t="shared" si="9"/>
@@ -16281,7 +16305,7 @@
       </c>
       <c r="AG150" s="4">
         <f t="shared" si="10"/>
-        <v>4764.24</v>
+        <v>4428.24</v>
       </c>
       <c r="AI150" t="s">
         <v>47</v>
@@ -16686,7 +16710,7 @@
       </c>
       <c r="M155" s="4">
         <f t="shared" si="11"/>
-        <v>14397.73</v>
+        <v>13831.73</v>
       </c>
       <c r="N155" s="4">
         <v>5377.9</v>
@@ -16695,7 +16719,7 @@
         <v>5016.9699999999993</v>
       </c>
       <c r="P155" s="4">
-        <v>1732.4299999999998</v>
+        <v>1166.4299999999998</v>
       </c>
       <c r="Q155" s="4">
         <v>2270.4299999999998</v>
@@ -16726,7 +16750,7 @@
       </c>
       <c r="AE155" s="4">
         <f t="shared" si="12"/>
-        <v>15347.73</v>
+        <v>14781.73</v>
       </c>
       <c r="AF155">
         <f t="shared" si="9"/>
@@ -16734,7 +16758,7 @@
       </c>
       <c r="AG155" s="4">
         <f t="shared" si="10"/>
-        <v>15347.73</v>
+        <v>14781.73</v>
       </c>
       <c r="AI155" t="s">
         <v>47</v>
@@ -17200,7 +17224,7 @@
       <c r="E161">
         <v>163</v>
       </c>
-      <c r="F161" t="s">
+      <c r="F161" s="8" t="s">
         <v>226</v>
       </c>
       <c r="G161" t="s">
@@ -17220,7 +17244,7 @@
       </c>
       <c r="M161" s="4">
         <f t="shared" si="11"/>
-        <v>7030.3099999999995</v>
+        <v>6746.15</v>
       </c>
       <c r="N161" s="4">
         <v>3356.8</v>
@@ -17229,7 +17253,7 @@
         <v>2275.8199999999997</v>
       </c>
       <c r="P161" s="4">
-        <v>836.66000000000008</v>
+        <v>552.5</v>
       </c>
       <c r="Q161" s="4">
         <v>561.03</v>
@@ -17252,7 +17276,7 @@
       <c r="X161" t="s">
         <v>36</v>
       </c>
-      <c r="Y161">
+      <c r="Y161" s="8">
         <v>15000</v>
       </c>
       <c r="AC161" t="s">
@@ -17263,7 +17287,7 @@
       </c>
       <c r="AE161" s="4">
         <f t="shared" si="12"/>
-        <v>7942.3099999999995</v>
+        <v>7658.15</v>
       </c>
       <c r="AF161">
         <f t="shared" si="9"/>
@@ -17271,7 +17295,7 @@
       </c>
       <c r="AG161" s="4">
         <f t="shared" si="10"/>
-        <v>22942.309999999998</v>
+        <v>22658.15</v>
       </c>
       <c r="AI161" t="s">
         <v>47</v>
@@ -17310,7 +17334,7 @@
       </c>
       <c r="M162" s="4">
         <f t="shared" si="11"/>
-        <v>4841.9999999999991</v>
+        <v>4179.1099999999997</v>
       </c>
       <c r="N162" s="4">
         <v>2302.75</v>
@@ -17319,7 +17343,7 @@
         <v>891.91</v>
       </c>
       <c r="P162" s="4">
-        <v>1351.73</v>
+        <v>688.83999999999992</v>
       </c>
       <c r="Q162" s="4">
         <v>295.61</v>
@@ -17350,7 +17374,7 @@
       </c>
       <c r="AE162" s="4">
         <f t="shared" si="12"/>
-        <v>5829.9999999999991</v>
+        <v>5167.1099999999997</v>
       </c>
       <c r="AF162">
         <f t="shared" si="9"/>
@@ -17358,7 +17382,7 @@
       </c>
       <c r="AG162" s="4">
         <f t="shared" si="10"/>
-        <v>5829.9999999999991</v>
+        <v>5167.1099999999997</v>
       </c>
       <c r="AI162" t="s">
         <v>47</v>
@@ -17929,7 +17953,7 @@
       <c r="E169">
         <v>172</v>
       </c>
-      <c r="F169" t="s">
+      <c r="F169" s="8" t="s">
         <v>423</v>
       </c>
       <c r="G169" t="s">
@@ -17981,7 +18005,7 @@
       <c r="X169" t="s">
         <v>36</v>
       </c>
-      <c r="Y169">
+      <c r="Y169" s="8">
         <v>15000</v>
       </c>
       <c r="AC169" t="s">
@@ -18405,7 +18429,7 @@
       </c>
       <c r="M174" s="4">
         <f t="shared" si="11"/>
-        <v>5807.5599999999995</v>
+        <v>5264.2</v>
       </c>
       <c r="N174" s="4">
         <v>2801.97</v>
@@ -18414,7 +18438,7 @@
         <v>1037.42</v>
       </c>
       <c r="P174" s="4">
-        <v>1643</v>
+        <v>1099.6400000000001</v>
       </c>
       <c r="Q174" s="4">
         <v>325.17</v>
@@ -18445,7 +18469,7 @@
       </c>
       <c r="AE174" s="4">
         <f t="shared" si="12"/>
-        <v>6719.5599999999995</v>
+        <v>6176.2</v>
       </c>
       <c r="AF174">
         <f t="shared" si="9"/>
@@ -18453,7 +18477,7 @@
       </c>
       <c r="AG174" s="4">
         <f t="shared" si="10"/>
-        <v>6719.5599999999995</v>
+        <v>6176.2</v>
       </c>
       <c r="AI174" t="s">
         <v>47</v>
@@ -18861,7 +18885,7 @@
       </c>
       <c r="M179" s="4">
         <f t="shared" si="11"/>
-        <v>11868.15</v>
+        <v>11845.51</v>
       </c>
       <c r="N179" s="4">
         <v>5377.9</v>
@@ -18870,7 +18894,7 @@
         <v>3870.92</v>
       </c>
       <c r="P179" s="4">
-        <v>892.93000000000006</v>
+        <v>870.29</v>
       </c>
       <c r="Q179" s="4">
         <v>1726.4</v>
@@ -18901,7 +18925,7 @@
       </c>
       <c r="AE179" s="4">
         <f t="shared" si="12"/>
-        <v>12742.15</v>
+        <v>12719.51</v>
       </c>
       <c r="AF179">
         <f t="shared" si="9"/>
@@ -18909,7 +18933,7 @@
       </c>
       <c r="AG179" s="4">
         <f t="shared" si="10"/>
-        <v>12742.15</v>
+        <v>12719.51</v>
       </c>
       <c r="AI179" t="s">
         <v>47</v>
@@ -19558,7 +19582,7 @@
       <c r="E187">
         <v>191</v>
       </c>
-      <c r="F187" t="s">
+      <c r="F187" s="8" t="s">
         <v>352</v>
       </c>
       <c r="G187" t="s">
@@ -19610,7 +19634,7 @@
       <c r="X187" t="s">
         <v>36</v>
       </c>
-      <c r="Y187">
+      <c r="Y187" s="8">
         <v>11000</v>
       </c>
       <c r="AC187" t="s">
@@ -20034,7 +20058,7 @@
       </c>
       <c r="M192" s="4">
         <f t="shared" si="11"/>
-        <v>12945.949999999997</v>
+        <v>12585.05</v>
       </c>
       <c r="N192" s="4">
         <v>5377.9</v>
@@ -20043,7 +20067,7 @@
         <v>4151.2299999999996</v>
       </c>
       <c r="P192" s="4">
-        <v>1403.2399999999998</v>
+        <v>1042.3399999999999</v>
       </c>
       <c r="Q192" s="4">
         <v>2013.58</v>
@@ -20074,7 +20098,7 @@
       </c>
       <c r="AE192" s="4">
         <f t="shared" si="12"/>
-        <v>13895.949999999997</v>
+        <v>13535.05</v>
       </c>
       <c r="AF192">
         <f t="shared" si="9"/>
@@ -20082,7 +20106,7 @@
       </c>
       <c r="AG192" s="4">
         <f t="shared" si="10"/>
-        <v>13895.949999999997</v>
+        <v>13535.05</v>
       </c>
       <c r="AI192" t="s">
         <v>47</v>
@@ -20124,7 +20148,7 @@
       </c>
       <c r="M193" s="4">
         <f t="shared" si="11"/>
-        <v>5307.57</v>
+        <v>5284.9299999999994</v>
       </c>
       <c r="N193" s="4">
         <v>2302.75</v>
@@ -20133,7 +20157,7 @@
         <v>1912.82</v>
       </c>
       <c r="P193" s="4">
-        <v>670.57999999999993</v>
+        <v>647.93999999999994</v>
       </c>
       <c r="Q193" s="4">
         <v>421.42</v>
@@ -20164,7 +20188,7 @@
       </c>
       <c r="AE193" s="4">
         <f t="shared" si="12"/>
-        <v>6219.57</v>
+        <v>6196.9299999999994</v>
       </c>
       <c r="AF193">
         <f t="shared" si="9"/>
@@ -20172,7 +20196,7 @@
       </c>
       <c r="AG193" s="4">
         <f t="shared" si="10"/>
-        <v>6219.57</v>
+        <v>6196.9299999999994</v>
       </c>
       <c r="AI193" t="s">
         <v>47</v>
@@ -20194,7 +20218,7 @@
       <c r="E194">
         <v>199</v>
       </c>
-      <c r="F194" t="s">
+      <c r="F194" s="8" t="s">
         <v>456</v>
       </c>
       <c r="G194" t="s">
@@ -20214,7 +20238,7 @@
       </c>
       <c r="M194" s="4">
         <f t="shared" si="11"/>
-        <v>10760.009999999998</v>
+        <v>10216.649999999998</v>
       </c>
       <c r="N194" s="4">
         <v>4681.28</v>
@@ -20223,7 +20247,7 @@
         <v>3199.44</v>
       </c>
       <c r="P194" s="4">
-        <v>1497.65</v>
+        <v>954.29</v>
       </c>
       <c r="Q194" s="4">
         <v>1381.6399999999999</v>
@@ -20246,7 +20270,7 @@
       <c r="X194" t="s">
         <v>36</v>
       </c>
-      <c r="Y194">
+      <c r="Y194" s="8">
         <v>15000</v>
       </c>
       <c r="AC194" t="s">
@@ -20257,7 +20281,7 @@
       </c>
       <c r="AE194" s="4">
         <f t="shared" si="12"/>
-        <v>11672.009999999998</v>
+        <v>11128.649999999998</v>
       </c>
       <c r="AF194">
         <f t="shared" si="9"/>
@@ -20265,7 +20289,7 @@
       </c>
       <c r="AG194" s="4">
         <f t="shared" si="10"/>
-        <v>26672.01</v>
+        <v>26128.649999999998</v>
       </c>
       <c r="AI194" t="s">
         <v>47</v>
@@ -20307,7 +20331,7 @@
       </c>
       <c r="M195" s="4">
         <f t="shared" si="11"/>
-        <v>6748.57</v>
+        <v>6176.89</v>
       </c>
       <c r="N195" s="4">
         <v>2302.75</v>
@@ -20316,7 +20340,7 @@
         <v>2179.75</v>
       </c>
       <c r="P195" s="4">
-        <v>1848.3200000000002</v>
+        <v>1276.6400000000001</v>
       </c>
       <c r="Q195" s="4">
         <v>417.75</v>
@@ -20347,7 +20371,7 @@
       </c>
       <c r="AE195" s="4">
         <f t="shared" si="12"/>
-        <v>7774.57</v>
+        <v>7202.89</v>
       </c>
       <c r="AF195">
         <f t="shared" ref="AF195:AF258" si="13">U195+Y195</f>
@@ -20355,7 +20379,7 @@
       </c>
       <c r="AG195" s="4">
         <f t="shared" ref="AG195:AG258" si="14">AF195+AE195</f>
-        <v>7774.57</v>
+        <v>7202.89</v>
       </c>
       <c r="AI195" t="s">
         <v>47</v>
@@ -20397,7 +20421,7 @@
       </c>
       <c r="M196" s="4">
         <f t="shared" ref="M196:M259" si="15">N196+O196+P196+Q196-S196+R196</f>
-        <v>6551.3000000000011</v>
+        <v>6049.59</v>
       </c>
       <c r="N196" s="4">
         <v>4416.3</v>
@@ -20406,7 +20430,7 @@
         <v>77.260000000000005</v>
       </c>
       <c r="P196" s="4">
-        <v>1655.87</v>
+        <v>1154.1599999999999</v>
       </c>
       <c r="Q196" s="4">
         <v>401.87</v>
@@ -20437,7 +20461,7 @@
       </c>
       <c r="AE196" s="4">
         <f t="shared" ref="AE196:AE259" si="16">M196+T196+V196</f>
-        <v>7235.3000000000011</v>
+        <v>6733.59</v>
       </c>
       <c r="AF196">
         <f t="shared" si="13"/>
@@ -20445,7 +20469,7 @@
       </c>
       <c r="AG196" s="4">
         <f t="shared" si="14"/>
-        <v>7235.3000000000011</v>
+        <v>6733.59</v>
       </c>
       <c r="AI196" t="s">
         <v>47</v>
@@ -20917,7 +20941,7 @@
       <c r="E202">
         <v>207</v>
       </c>
-      <c r="F202" t="s">
+      <c r="F202" s="6" t="s">
         <v>315</v>
       </c>
       <c r="G202" t="s">
@@ -21193,7 +21217,7 @@
       <c r="E205">
         <v>210</v>
       </c>
-      <c r="F205" t="s">
+      <c r="F205" s="8" t="s">
         <v>375</v>
       </c>
       <c r="G205" t="s">
@@ -21213,7 +21237,7 @@
       </c>
       <c r="M205" s="4">
         <f t="shared" si="15"/>
-        <v>6650.9500000000007</v>
+        <v>6084.9500000000007</v>
       </c>
       <c r="N205" s="4">
         <v>3356.8</v>
@@ -21222,7 +21246,7 @@
         <v>1894.5000000000002</v>
       </c>
       <c r="P205" s="4">
-        <v>888.64</v>
+        <v>322.64</v>
       </c>
       <c r="Q205" s="4">
         <v>511.01</v>
@@ -21245,7 +21269,7 @@
       <c r="X205" t="s">
         <v>36</v>
       </c>
-      <c r="Y205">
+      <c r="Y205" s="8">
         <v>15000</v>
       </c>
       <c r="AC205" t="s">
@@ -21256,7 +21280,7 @@
       </c>
       <c r="AE205" s="4">
         <f t="shared" si="16"/>
-        <v>7600.9500000000007</v>
+        <v>7034.9500000000007</v>
       </c>
       <c r="AF205">
         <f t="shared" si="13"/>
@@ -21264,7 +21288,7 @@
       </c>
       <c r="AG205" s="4">
         <f t="shared" si="14"/>
-        <v>22600.95</v>
+        <v>22034.95</v>
       </c>
       <c r="AI205" t="s">
         <v>47</v>
@@ -21428,7 +21452,7 @@
       <c r="X207" t="s">
         <v>36</v>
       </c>
-      <c r="Y207">
+      <c r="Y207" s="8">
         <v>5000</v>
       </c>
       <c r="AC207" t="s">
@@ -21652,7 +21676,7 @@
       <c r="E210">
         <v>215</v>
       </c>
-      <c r="F210" t="s">
+      <c r="F210" s="8" t="s">
         <v>133</v>
       </c>
       <c r="G210" t="s">
@@ -21704,7 +21728,7 @@
       <c r="X210" t="s">
         <v>36</v>
       </c>
-      <c r="Y210">
+      <c r="Y210" s="8">
         <v>11000</v>
       </c>
       <c r="AC210" t="s">
@@ -21765,7 +21789,7 @@
       </c>
       <c r="M211" s="4">
         <f t="shared" si="15"/>
-        <v>7269.8099999999995</v>
+        <v>7247.17</v>
       </c>
       <c r="N211" s="4">
         <v>2801.97</v>
@@ -21774,7 +21798,7 @@
         <v>2902.9</v>
       </c>
       <c r="P211" s="4">
-        <v>870.56999999999994</v>
+        <v>847.93</v>
       </c>
       <c r="Q211" s="4">
         <v>694.37</v>
@@ -21805,7 +21829,7 @@
       </c>
       <c r="AE211" s="4">
         <f t="shared" si="16"/>
-        <v>8219.81</v>
+        <v>8197.17</v>
       </c>
       <c r="AF211">
         <f t="shared" si="13"/>
@@ -21813,7 +21837,7 @@
       </c>
       <c r="AG211" s="4">
         <f t="shared" si="14"/>
-        <v>8219.81</v>
+        <v>8197.17</v>
       </c>
       <c r="AI211" t="s">
         <v>47</v>
@@ -21855,7 +21879,7 @@
       </c>
       <c r="M212" s="4">
         <f t="shared" si="15"/>
-        <v>6397.49</v>
+        <v>6082.6999999999989</v>
       </c>
       <c r="N212" s="4">
         <v>3356.8</v>
@@ -21864,7 +21888,7 @@
         <v>1474.1699999999998</v>
       </c>
       <c r="P212" s="4">
-        <v>1112.8699999999999</v>
+        <v>798.07999999999993</v>
       </c>
       <c r="Q212" s="4">
         <v>453.65</v>
@@ -21887,7 +21911,7 @@
       <c r="X212" t="s">
         <v>36</v>
       </c>
-      <c r="Y212">
+      <c r="Y212" s="8">
         <v>10000</v>
       </c>
       <c r="AC212" t="s">
@@ -21898,7 +21922,7 @@
       </c>
       <c r="AE212" s="4">
         <f t="shared" si="16"/>
-        <v>7385.49</v>
+        <v>7070.6999999999989</v>
       </c>
       <c r="AF212">
         <f t="shared" si="13"/>
@@ -21906,7 +21930,7 @@
       </c>
       <c r="AG212" s="4">
         <f t="shared" si="14"/>
-        <v>17385.489999999998</v>
+        <v>17070.699999999997</v>
       </c>
       <c r="AI212" t="s">
         <v>47</v>
@@ -21948,7 +21972,7 @@
       </c>
       <c r="M213" s="4">
         <f t="shared" si="15"/>
-        <v>15604.469999999998</v>
+        <v>14794.629999999997</v>
       </c>
       <c r="N213" s="4">
         <v>5377.9</v>
@@ -21957,7 +21981,7 @@
         <v>5507.72</v>
       </c>
       <c r="P213" s="4">
-        <v>2491.3900000000003</v>
+        <v>1681.5500000000002</v>
       </c>
       <c r="Q213" s="4">
         <v>2227.46</v>
@@ -21988,7 +22012,7 @@
       </c>
       <c r="AE213" s="4">
         <f t="shared" si="16"/>
-        <v>16592.469999999998</v>
+        <v>15782.629999999997</v>
       </c>
       <c r="AF213">
         <f t="shared" si="13"/>
@@ -21996,7 +22020,7 @@
       </c>
       <c r="AG213" s="4">
         <f t="shared" si="14"/>
-        <v>16592.469999999998</v>
+        <v>15782.629999999997</v>
       </c>
       <c r="AI213" t="s">
         <v>47</v>
@@ -22128,7 +22152,7 @@
       </c>
       <c r="M215" s="4">
         <f t="shared" si="15"/>
-        <v>6408.35</v>
+        <v>6029.91</v>
       </c>
       <c r="N215" s="4">
         <v>2302.75</v>
@@ -22137,7 +22161,7 @@
         <v>2351.34</v>
       </c>
       <c r="P215" s="4">
-        <v>1273.31</v>
+        <v>894.86999999999989</v>
       </c>
       <c r="Q215" s="4">
         <v>480.95</v>
@@ -22168,7 +22192,7 @@
       </c>
       <c r="AE215" s="4">
         <f t="shared" si="16"/>
-        <v>7358.35</v>
+        <v>6979.91</v>
       </c>
       <c r="AF215">
         <f t="shared" si="13"/>
@@ -22176,7 +22200,7 @@
       </c>
       <c r="AG215" s="4">
         <f t="shared" si="14"/>
-        <v>7358.35</v>
+        <v>6979.91</v>
       </c>
       <c r="AI215" t="s">
         <v>47</v>
@@ -22305,7 +22329,7 @@
       </c>
       <c r="M217" s="4">
         <f t="shared" si="15"/>
-        <v>6855.75</v>
+        <v>5602.25</v>
       </c>
       <c r="N217" s="4">
         <v>2819.39</v>
@@ -22314,7 +22338,7 @@
         <v>1086.31</v>
       </c>
       <c r="P217" s="4">
-        <v>2609.34</v>
+        <v>1355.8400000000001</v>
       </c>
       <c r="Q217" s="4">
         <v>340.71</v>
@@ -22345,7 +22369,7 @@
       </c>
       <c r="AE217" s="4">
         <f t="shared" si="16"/>
-        <v>7805.75</v>
+        <v>6552.25</v>
       </c>
       <c r="AF217">
         <f t="shared" si="13"/>
@@ -22353,7 +22377,7 @@
       </c>
       <c r="AG217" s="4">
         <f t="shared" si="14"/>
-        <v>7805.75</v>
+        <v>6552.25</v>
       </c>
       <c r="AI217" t="s">
         <v>47</v>
@@ -22395,7 +22419,7 @@
       </c>
       <c r="M218" s="4">
         <f t="shared" si="15"/>
-        <v>4869.0599999999995</v>
+        <v>4103.82</v>
       </c>
       <c r="N218" s="4">
         <v>2664.74</v>
@@ -22404,7 +22428,7 @@
         <v>14.28</v>
       </c>
       <c r="P218" s="4">
-        <v>1945.6000000000001</v>
+        <v>1180.3600000000001</v>
       </c>
       <c r="Q218" s="4">
         <v>244.44</v>
@@ -22435,7 +22459,7 @@
       </c>
       <c r="AE218" s="4">
         <f t="shared" si="16"/>
-        <v>4869.0599999999995</v>
+        <v>4103.82</v>
       </c>
       <c r="AF218">
         <f t="shared" si="13"/>
@@ -22443,7 +22467,7 @@
       </c>
       <c r="AG218" s="4">
         <f t="shared" si="14"/>
-        <v>4869.0599999999995</v>
+        <v>4103.82</v>
       </c>
       <c r="AI218" t="s">
         <v>39</v>
@@ -23011,7 +23035,7 @@
       <c r="E225">
         <v>230</v>
       </c>
-      <c r="F225" t="s">
+      <c r="F225" s="8" t="s">
         <v>350</v>
       </c>
       <c r="G225" t="s">
@@ -23063,7 +23087,7 @@
       <c r="X225" t="s">
         <v>36</v>
       </c>
-      <c r="Y225">
+      <c r="Y225" s="8">
         <v>15000</v>
       </c>
       <c r="AC225" t="s">
@@ -23403,7 +23427,7 @@
       </c>
       <c r="M229" s="4">
         <f t="shared" si="15"/>
-        <v>11475.48</v>
+        <v>10640.28</v>
       </c>
       <c r="N229" s="4">
         <v>5114.5</v>
@@ -23412,7 +23436,7 @@
         <v>3453.8300000000004</v>
       </c>
       <c r="P229" s="4">
-        <v>1670.4</v>
+        <v>835.2</v>
       </c>
       <c r="Q229" s="4">
         <v>1236.75</v>
@@ -23443,7 +23467,7 @@
       </c>
       <c r="AE229" s="4">
         <f t="shared" si="16"/>
-        <v>11475.48</v>
+        <v>10640.28</v>
       </c>
       <c r="AF229">
         <f t="shared" si="13"/>
@@ -23451,7 +23475,7 @@
       </c>
       <c r="AG229" s="4">
         <f t="shared" si="14"/>
-        <v>11475.48</v>
+        <v>10640.28</v>
       </c>
       <c r="AI229" t="s">
         <v>47</v>
@@ -23676,7 +23700,7 @@
       </c>
       <c r="M232" s="4">
         <f t="shared" si="15"/>
-        <v>5413.69</v>
+        <v>5129.53</v>
       </c>
       <c r="N232" s="4">
         <v>2801.97</v>
@@ -23685,7 +23709,7 @@
         <v>1109.94</v>
       </c>
       <c r="P232" s="4">
-        <v>1121.48</v>
+        <v>837.32</v>
       </c>
       <c r="Q232" s="4">
         <v>380.3</v>
@@ -23716,7 +23740,7 @@
       </c>
       <c r="AE232" s="4">
         <f t="shared" si="16"/>
-        <v>6325.69</v>
+        <v>6041.53</v>
       </c>
       <c r="AF232">
         <f t="shared" si="13"/>
@@ -23724,7 +23748,7 @@
       </c>
       <c r="AG232" s="4">
         <f t="shared" si="14"/>
-        <v>6325.69</v>
+        <v>6041.53</v>
       </c>
       <c r="AI232" t="s">
         <v>47</v>
@@ -24315,7 +24339,7 @@
       </c>
       <c r="M239" s="4">
         <f t="shared" si="15"/>
-        <v>5576.5400000000009</v>
+        <v>5076.2200000000012</v>
       </c>
       <c r="N239" s="4">
         <v>2302.75</v>
@@ -24324,7 +24348,7 @@
         <v>1508.45</v>
       </c>
       <c r="P239" s="4">
-        <v>1394.45</v>
+        <v>894.13</v>
       </c>
       <c r="Q239" s="4">
         <v>370.89</v>
@@ -24355,7 +24379,7 @@
       </c>
       <c r="AE239" s="4">
         <f t="shared" si="16"/>
-        <v>6450.5400000000009</v>
+        <v>5950.2200000000012</v>
       </c>
       <c r="AF239">
         <f t="shared" si="13"/>
@@ -24363,7 +24387,7 @@
       </c>
       <c r="AG239" s="4">
         <f t="shared" si="14"/>
-        <v>6450.5400000000009</v>
+        <v>5950.2200000000012</v>
       </c>
       <c r="AI239" t="s">
         <v>47</v>
@@ -25044,7 +25068,7 @@
       </c>
       <c r="M247" s="4">
         <f t="shared" si="15"/>
-        <v>6776.65</v>
+        <v>6210.65</v>
       </c>
       <c r="N247" s="4">
         <v>2801.97</v>
@@ -25053,7 +25077,7 @@
         <v>2029.42</v>
       </c>
       <c r="P247" s="4">
-        <v>1441.18</v>
+        <v>875.18000000000006</v>
       </c>
       <c r="Q247" s="4">
         <v>504.08</v>
@@ -25084,7 +25108,7 @@
       </c>
       <c r="AE247" s="4">
         <f t="shared" si="16"/>
-        <v>7726.65</v>
+        <v>7160.65</v>
       </c>
       <c r="AF247">
         <f t="shared" si="13"/>
@@ -25092,7 +25116,7 @@
       </c>
       <c r="AG247" s="4">
         <f t="shared" si="14"/>
-        <v>7726.65</v>
+        <v>7160.65</v>
       </c>
       <c r="AI247" t="s">
         <v>47</v>
@@ -25134,7 +25158,7 @@
       </c>
       <c r="M248" s="4">
         <f t="shared" si="15"/>
-        <v>7355.53</v>
+        <v>6450.9699999999993</v>
       </c>
       <c r="N248" s="4">
         <v>2819.39</v>
@@ -25143,7 +25167,7 @@
         <v>1819.3400000000001</v>
       </c>
       <c r="P248" s="4">
-        <v>2285.1999999999998</v>
+        <v>1380.6399999999999</v>
       </c>
       <c r="Q248" s="4">
         <v>431.6</v>
@@ -25174,7 +25198,7 @@
       </c>
       <c r="AE248" s="4">
         <f t="shared" si="16"/>
-        <v>8381.5299999999988</v>
+        <v>7476.9699999999993</v>
       </c>
       <c r="AF248">
         <f t="shared" si="13"/>
@@ -25182,7 +25206,7 @@
       </c>
       <c r="AG248" s="4">
         <f t="shared" si="14"/>
-        <v>8381.5299999999988</v>
+        <v>7476.9699999999993</v>
       </c>
       <c r="AI248" t="s">
         <v>47</v>
@@ -25593,7 +25617,7 @@
       </c>
       <c r="M253" s="4">
         <f t="shared" si="15"/>
-        <v>4701.18</v>
+        <v>4078.51</v>
       </c>
       <c r="N253" s="4">
         <v>2786.48</v>
@@ -25602,7 +25626,7 @@
         <v>477.49</v>
       </c>
       <c r="P253" s="4">
-        <v>1173.31</v>
+        <v>550.64</v>
       </c>
       <c r="Q253" s="4">
         <v>263.89999999999998</v>
@@ -25633,7 +25657,7 @@
       </c>
       <c r="AE253" s="4">
         <f t="shared" si="16"/>
-        <v>5613.18</v>
+        <v>4990.51</v>
       </c>
       <c r="AF253">
         <f t="shared" si="13"/>
@@ -25641,7 +25665,7 @@
       </c>
       <c r="AG253" s="4">
         <f t="shared" si="14"/>
-        <v>5613.18</v>
+        <v>4990.51</v>
       </c>
       <c r="AI253" t="s">
         <v>39</v>
@@ -25773,7 +25797,7 @@
       </c>
       <c r="M255" s="4">
         <f t="shared" si="15"/>
-        <v>5196.53</v>
+        <v>4630.53</v>
       </c>
       <c r="N255" s="4">
         <v>2302.75</v>
@@ -25782,7 +25806,7 @@
         <v>1451.04</v>
       </c>
       <c r="P255" s="4">
-        <v>1078.32</v>
+        <v>512.31999999999994</v>
       </c>
       <c r="Q255" s="4">
         <v>364.42</v>
@@ -25813,7 +25837,7 @@
       </c>
       <c r="AE255" s="4">
         <f t="shared" si="16"/>
-        <v>6146.53</v>
+        <v>5580.53</v>
       </c>
       <c r="AF255">
         <f t="shared" si="13"/>
@@ -25821,7 +25845,7 @@
       </c>
       <c r="AG255" s="4">
         <f t="shared" si="14"/>
-        <v>6146.53</v>
+        <v>5580.53</v>
       </c>
       <c r="AI255" t="s">
         <v>47</v>
@@ -26046,7 +26070,7 @@
       </c>
       <c r="M258" s="4">
         <f t="shared" si="15"/>
-        <v>6554.35</v>
+        <v>5697.35</v>
       </c>
       <c r="N258" s="4">
         <v>2819.39</v>
@@ -26055,7 +26079,7 @@
         <v>1170.29</v>
       </c>
       <c r="P258" s="4">
-        <v>2201.08</v>
+        <v>1344.08</v>
       </c>
       <c r="Q258" s="4">
         <v>363.59</v>
@@ -26086,7 +26110,7 @@
       </c>
       <c r="AE258" s="4">
         <f t="shared" si="16"/>
-        <v>7504.35</v>
+        <v>6647.35</v>
       </c>
       <c r="AF258">
         <f t="shared" si="13"/>
@@ -26094,7 +26118,7 @@
       </c>
       <c r="AG258" s="4">
         <f t="shared" si="14"/>
-        <v>7504.35</v>
+        <v>6647.35</v>
       </c>
       <c r="AI258" t="s">
         <v>39</v>
@@ -26133,7 +26157,7 @@
       </c>
       <c r="M259" s="4">
         <f t="shared" si="15"/>
-        <v>6142.48</v>
+        <v>5821.49</v>
       </c>
       <c r="N259" s="4">
         <v>2801.97</v>
@@ -26142,7 +26166,7 @@
         <v>1692.5599999999997</v>
       </c>
       <c r="P259" s="4">
-        <v>1191.03</v>
+        <v>870.04</v>
       </c>
       <c r="Q259" s="4">
         <v>456.92</v>
@@ -26173,7 +26197,7 @@
       </c>
       <c r="AE259" s="4">
         <f t="shared" si="16"/>
-        <v>7092.48</v>
+        <v>6771.49</v>
       </c>
       <c r="AF259">
         <f t="shared" ref="AF259:AF322" si="17">U259+Y259</f>
@@ -26181,7 +26205,7 @@
       </c>
       <c r="AG259" s="4">
         <f t="shared" ref="AG259:AG322" si="18">AF259+AE259</f>
-        <v>7092.48</v>
+        <v>6771.49</v>
       </c>
       <c r="AI259" t="s">
         <v>47</v>
@@ -26223,7 +26247,7 @@
       </c>
       <c r="M260" s="4">
         <f t="shared" ref="M260:M323" si="19">N260+O260+P260+Q260-S260+R260</f>
-        <v>4924.6100000000006</v>
+        <v>4901.97</v>
       </c>
       <c r="N260" s="4">
         <v>2819.39</v>
@@ -26232,7 +26256,7 @@
         <v>1112.3700000000001</v>
       </c>
       <c r="P260" s="4">
-        <v>649.04</v>
+        <v>626.4</v>
       </c>
       <c r="Q260" s="4">
         <v>343.81</v>
@@ -26263,7 +26287,7 @@
       </c>
       <c r="AE260" s="4">
         <f t="shared" ref="AE260:AE323" si="20">M260+T260+V260</f>
-        <v>5874.6100000000006</v>
+        <v>5851.97</v>
       </c>
       <c r="AF260">
         <f t="shared" si="17"/>
@@ -26271,7 +26295,7 @@
       </c>
       <c r="AG260" s="4">
         <f t="shared" si="18"/>
-        <v>5874.6100000000006</v>
+        <v>5851.97</v>
       </c>
       <c r="AI260" t="s">
         <v>39</v>
@@ -26528,7 +26552,7 @@
       <c r="X263" t="s">
         <v>36</v>
       </c>
-      <c r="Y263">
+      <c r="Y263" s="8">
         <v>5000</v>
       </c>
       <c r="AC263" t="s">
@@ -26755,7 +26779,7 @@
       <c r="E266">
         <v>275</v>
       </c>
-      <c r="F266" t="s">
+      <c r="F266" s="8" t="s">
         <v>157</v>
       </c>
       <c r="G266" t="s">
@@ -26807,7 +26831,7 @@
       <c r="X266" t="s">
         <v>36</v>
       </c>
-      <c r="Y266">
+      <c r="Y266" s="8">
         <v>15000</v>
       </c>
       <c r="AC266" t="s">
@@ -26868,7 +26892,7 @@
       </c>
       <c r="M267" s="4">
         <f t="shared" si="19"/>
-        <v>5481.84</v>
+        <v>5190.84</v>
       </c>
       <c r="N267" s="4">
         <v>2302.75</v>
@@ -26877,7 +26901,7 @@
         <v>1710.53</v>
       </c>
       <c r="P267" s="4">
-        <v>1073</v>
+        <v>782</v>
       </c>
       <c r="Q267" s="4">
         <v>395.56</v>
@@ -26908,7 +26932,7 @@
       </c>
       <c r="AE267" s="4">
         <f t="shared" si="20"/>
-        <v>6431.84</v>
+        <v>6140.84</v>
       </c>
       <c r="AF267">
         <f t="shared" si="17"/>
@@ -26916,7 +26940,7 @@
       </c>
       <c r="AG267" s="4">
         <f t="shared" si="18"/>
-        <v>6431.84</v>
+        <v>6140.84</v>
       </c>
       <c r="AI267" t="s">
         <v>47</v>
@@ -26955,7 +26979,7 @@
       </c>
       <c r="M268" s="4">
         <f t="shared" si="19"/>
-        <v>5101.62</v>
+        <v>5008.78</v>
       </c>
       <c r="N268" s="4">
         <v>2801.97</v>
@@ -26964,7 +26988,7 @@
         <v>982.77</v>
       </c>
       <c r="P268" s="4">
-        <v>973.12</v>
+        <v>880.28</v>
       </c>
       <c r="Q268" s="4">
         <v>343.76</v>
@@ -26995,7 +27019,7 @@
       </c>
       <c r="AE268" s="4">
         <f t="shared" si="20"/>
-        <v>6013.62</v>
+        <v>5920.78</v>
       </c>
       <c r="AF268">
         <f t="shared" si="17"/>
@@ -27003,7 +27027,7 @@
       </c>
       <c r="AG268" s="4">
         <f t="shared" si="18"/>
-        <v>6013.62</v>
+        <v>5920.78</v>
       </c>
       <c r="AI268" t="s">
         <v>47</v>
@@ -27205,7 +27229,7 @@
       <c r="E271">
         <v>280</v>
       </c>
-      <c r="F271" t="s">
+      <c r="F271" s="8" t="s">
         <v>250</v>
       </c>
       <c r="G271" t="s">
@@ -27260,7 +27284,7 @@
       <c r="X271">
         <v>0</v>
       </c>
-      <c r="Y271">
+      <c r="Y271" s="8">
         <v>2900</v>
       </c>
       <c r="AC271" t="s">
@@ -27321,7 +27345,7 @@
       </c>
       <c r="M272" s="4">
         <f t="shared" si="19"/>
-        <v>4481.88</v>
+        <v>3934.85</v>
       </c>
       <c r="N272" s="4">
         <v>2302.75</v>
@@ -27330,7 +27354,7 @@
         <v>362.66</v>
       </c>
       <c r="P272" s="4">
-        <v>1581.8700000000001</v>
+        <v>1034.8399999999999</v>
       </c>
       <c r="Q272" s="4">
         <v>234.6</v>
@@ -27361,7 +27385,7 @@
       </c>
       <c r="AE272" s="4">
         <f t="shared" si="20"/>
-        <v>5355.88</v>
+        <v>4808.8500000000004</v>
       </c>
       <c r="AF272">
         <f t="shared" si="17"/>
@@ -27369,7 +27393,7 @@
       </c>
       <c r="AG272" s="4">
         <f t="shared" si="18"/>
-        <v>5355.88</v>
+        <v>4808.8500000000004</v>
       </c>
       <c r="AI272" t="s">
         <v>47</v>
@@ -27757,7 +27781,7 @@
       <c r="E277">
         <v>286</v>
       </c>
-      <c r="F277" t="s">
+      <c r="F277" s="8" t="s">
         <v>430</v>
       </c>
       <c r="G277" t="s">
@@ -27809,7 +27833,7 @@
       <c r="X277" t="s">
         <v>36</v>
       </c>
-      <c r="Y277">
+      <c r="Y277" s="8">
         <v>15000</v>
       </c>
       <c r="AC277" t="s">
@@ -28326,7 +28350,7 @@
       </c>
       <c r="M283" s="4">
         <f t="shared" si="19"/>
-        <v>5774.9000000000005</v>
+        <v>5281.1</v>
       </c>
       <c r="N283" s="4">
         <v>3195.53</v>
@@ -28335,7 +28359,7 @@
         <v>921.32999999999993</v>
       </c>
       <c r="P283" s="4">
-        <v>1294.2</v>
+        <v>800.4</v>
       </c>
       <c r="Q283" s="4">
         <v>363.84</v>
@@ -28366,7 +28390,7 @@
       </c>
       <c r="AE283" s="4">
         <f t="shared" si="20"/>
-        <v>6686.9000000000005</v>
+        <v>6193.1</v>
       </c>
       <c r="AF283">
         <f t="shared" si="17"/>
@@ -28374,7 +28398,7 @@
       </c>
       <c r="AG283" s="4">
         <f t="shared" si="18"/>
-        <v>6686.9000000000005</v>
+        <v>6193.1</v>
       </c>
       <c r="AI283" t="s">
         <v>47</v>
@@ -28596,7 +28620,7 @@
       </c>
       <c r="M286" s="4">
         <f t="shared" si="19"/>
-        <v>3673.6299999999997</v>
+        <v>3334.0299999999997</v>
       </c>
       <c r="N286" s="4">
         <v>2302.75</v>
@@ -28605,7 +28629,7 @@
         <v>259.83</v>
       </c>
       <c r="P286" s="4">
-        <v>911.91000000000008</v>
+        <v>572.30999999999995</v>
       </c>
       <c r="Q286" s="4">
         <v>199.14</v>
@@ -28630,7 +28654,7 @@
       </c>
       <c r="AE286" s="4">
         <f t="shared" si="20"/>
-        <v>4243.6299999999992</v>
+        <v>3904.0299999999997</v>
       </c>
       <c r="AF286">
         <f t="shared" si="17"/>
@@ -28638,7 +28662,7 @@
       </c>
       <c r="AG286" s="4">
         <f t="shared" si="18"/>
-        <v>4243.6299999999992</v>
+        <v>3904.0299999999997</v>
       </c>
       <c r="AI286" t="s">
         <v>47</v>
@@ -28683,7 +28707,7 @@
       </c>
       <c r="M287" s="4">
         <f t="shared" si="19"/>
-        <v>4831.9400000000005</v>
+        <v>4552.58</v>
       </c>
       <c r="N287" s="4">
         <v>2302.75</v>
@@ -28692,7 +28716,7 @@
         <v>1122.78</v>
       </c>
       <c r="P287" s="4">
-        <v>1085.1400000000001</v>
+        <v>805.78</v>
       </c>
       <c r="Q287" s="4">
         <v>321.27</v>
@@ -28717,7 +28741,7 @@
       </c>
       <c r="AE287" s="4">
         <f t="shared" si="20"/>
-        <v>5743.9400000000005</v>
+        <v>5464.58</v>
       </c>
       <c r="AF287">
         <f t="shared" si="17"/>
@@ -28725,7 +28749,7 @@
       </c>
       <c r="AG287" s="4">
         <f t="shared" si="18"/>
-        <v>5743.9400000000005</v>
+        <v>5464.58</v>
       </c>
       <c r="AI287" t="s">
         <v>47</v>
@@ -28770,7 +28794,7 @@
       </c>
       <c r="M288" s="4">
         <f t="shared" si="19"/>
-        <v>5791.96</v>
+        <v>5248.98</v>
       </c>
       <c r="N288" s="4">
         <v>2302.75</v>
@@ -28779,7 +28803,7 @@
         <v>1657.36</v>
       </c>
       <c r="P288" s="4">
-        <v>1440.8400000000001</v>
+        <v>897.8599999999999</v>
       </c>
       <c r="Q288" s="4">
         <v>391.01</v>
@@ -28804,7 +28828,7 @@
       </c>
       <c r="AE288" s="4">
         <f t="shared" si="20"/>
-        <v>6855.96</v>
+        <v>6312.98</v>
       </c>
       <c r="AF288">
         <f t="shared" si="17"/>
@@ -28812,7 +28836,7 @@
       </c>
       <c r="AG288" s="4">
         <f t="shared" si="18"/>
-        <v>6855.96</v>
+        <v>6312.98</v>
       </c>
       <c r="AI288" t="s">
         <v>47</v>
@@ -29025,7 +29049,7 @@
       </c>
       <c r="M291" s="4">
         <f t="shared" si="19"/>
-        <v>6472.3234549999988</v>
+        <v>6438.0434549999991</v>
       </c>
       <c r="N291" s="4">
         <v>2302.753455</v>
@@ -29034,7 +29058,7 @@
         <v>2326.39</v>
       </c>
       <c r="P291" s="4">
-        <v>1365.48</v>
+        <v>1331.2</v>
       </c>
       <c r="Q291" s="4">
         <v>477.7</v>
@@ -29059,7 +29083,7 @@
       </c>
       <c r="AE291" s="4">
         <f t="shared" si="20"/>
-        <v>7498.3234549999988</v>
+        <v>7464.0434549999991</v>
       </c>
       <c r="AF291">
         <f t="shared" si="17"/>
@@ -29067,7 +29091,7 @@
       </c>
       <c r="AG291" s="4">
         <f t="shared" si="18"/>
-        <v>7498.3234549999988</v>
+        <v>7464.0434549999991</v>
       </c>
       <c r="AI291" t="s">
         <v>47</v>
@@ -29109,7 +29133,7 @@
       </c>
       <c r="M292" s="4">
         <f t="shared" si="19"/>
-        <v>6301.829999999999</v>
+        <v>5732.07</v>
       </c>
       <c r="N292" s="4">
         <v>2302.75</v>
@@ -29118,7 +29142,7 @@
         <v>1915.61</v>
       </c>
       <c r="P292" s="4">
-        <v>1662.32</v>
+        <v>1092.56</v>
       </c>
       <c r="Q292" s="4">
         <v>421.15</v>
@@ -29143,7 +29167,7 @@
       </c>
       <c r="AE292" s="4">
         <f t="shared" si="20"/>
-        <v>7365.829999999999</v>
+        <v>6796.07</v>
       </c>
       <c r="AF292">
         <f t="shared" si="17"/>
@@ -29151,7 +29175,7 @@
       </c>
       <c r="AG292" s="4">
         <f t="shared" si="18"/>
-        <v>7365.829999999999</v>
+        <v>6796.07</v>
       </c>
       <c r="AI292" t="s">
         <v>47</v>
@@ -29193,7 +29217,7 @@
       </c>
       <c r="M293" s="4">
         <f t="shared" si="19"/>
-        <v>5525.55</v>
+        <v>5327.67</v>
       </c>
       <c r="N293" s="4">
         <v>2302.75</v>
@@ -29202,7 +29226,7 @@
         <v>1883.01</v>
       </c>
       <c r="P293" s="4">
-        <v>922.55</v>
+        <v>724.67</v>
       </c>
       <c r="Q293" s="4">
         <v>417.24</v>
@@ -29227,7 +29251,7 @@
       </c>
       <c r="AE293" s="4">
         <f t="shared" si="20"/>
-        <v>6437.55</v>
+        <v>6239.67</v>
       </c>
       <c r="AF293">
         <f t="shared" si="17"/>
@@ -29235,7 +29259,7 @@
       </c>
       <c r="AG293" s="4">
         <f t="shared" si="18"/>
-        <v>6437.55</v>
+        <v>6239.67</v>
       </c>
       <c r="AI293" t="s">
         <v>47</v>
@@ -29277,7 +29301,7 @@
       </c>
       <c r="M294" s="4">
         <f t="shared" si="19"/>
-        <v>6569.7000000000007</v>
+        <v>6239.31</v>
       </c>
       <c r="N294" s="4">
         <v>2801.97</v>
@@ -29286,7 +29310,7 @@
         <v>1718.5700000000002</v>
       </c>
       <c r="P294" s="4">
-        <v>1588.65</v>
+        <v>1258.26</v>
       </c>
       <c r="Q294" s="4">
         <v>460.51</v>
@@ -29311,7 +29335,7 @@
       </c>
       <c r="AE294" s="4">
         <f t="shared" si="20"/>
-        <v>7557.7000000000007</v>
+        <v>7227.31</v>
       </c>
       <c r="AF294">
         <f t="shared" si="17"/>
@@ -29319,7 +29343,7 @@
       </c>
       <c r="AG294" s="4">
         <f t="shared" si="18"/>
-        <v>7557.7000000000007</v>
+        <v>7227.31</v>
       </c>
       <c r="AI294" t="s">
         <v>47</v>
@@ -29445,7 +29469,7 @@
       </c>
       <c r="M296" s="4">
         <f t="shared" si="19"/>
-        <v>6414.8899999999994</v>
+        <v>6054.65</v>
       </c>
       <c r="N296" s="4">
         <v>2302.75</v>
@@ -29454,7 +29478,7 @@
         <v>2227.7599999999998</v>
       </c>
       <c r="P296" s="4">
-        <v>1439.48</v>
+        <v>1079.24</v>
       </c>
       <c r="Q296" s="4">
         <v>444.9</v>
@@ -29479,7 +29503,7 @@
       </c>
       <c r="AE296" s="4">
         <f t="shared" si="20"/>
-        <v>7402.8899999999994</v>
+        <v>7042.65</v>
       </c>
       <c r="AF296">
         <f t="shared" si="17"/>
@@ -29487,7 +29511,7 @@
       </c>
       <c r="AG296" s="4">
         <f t="shared" si="18"/>
-        <v>7402.8899999999994</v>
+        <v>7042.65</v>
       </c>
       <c r="AI296" t="s">
         <v>47</v>
@@ -29529,7 +29553,7 @@
       </c>
       <c r="M297" s="4">
         <f t="shared" si="19"/>
-        <v>4930.1999999999989</v>
+        <v>4778.5599999999995</v>
       </c>
       <c r="N297" s="4">
         <v>2801.97</v>
@@ -29538,7 +29562,7 @@
         <v>1062.01</v>
       </c>
       <c r="P297" s="4">
-        <v>712.81999999999994</v>
+        <v>561.17999999999995</v>
       </c>
       <c r="Q297" s="4">
         <v>353.4</v>
@@ -29563,7 +29587,7 @@
       </c>
       <c r="AE297" s="4">
         <f t="shared" si="20"/>
-        <v>5538.1999999999989</v>
+        <v>5386.5599999999995</v>
       </c>
       <c r="AF297">
         <f t="shared" si="17"/>
@@ -29571,7 +29595,7 @@
       </c>
       <c r="AG297" s="4">
         <f t="shared" si="18"/>
-        <v>5538.1999999999989</v>
+        <v>5386.5599999999995</v>
       </c>
       <c r="AI297" t="s">
         <v>47</v>
@@ -29613,7 +29637,7 @@
       </c>
       <c r="M298" s="4">
         <f t="shared" si="19"/>
-        <v>7542.93</v>
+        <v>6583.09</v>
       </c>
       <c r="N298" s="4">
         <v>2801.97</v>
@@ -29622,7 +29646,7 @@
         <v>1945.54</v>
       </c>
       <c r="P298" s="4">
-        <v>2303.08</v>
+        <v>1343.24</v>
       </c>
       <c r="Q298" s="4">
         <v>492.34</v>
@@ -29647,7 +29671,7 @@
       </c>
       <c r="AE298" s="4">
         <f t="shared" si="20"/>
-        <v>8606.93</v>
+        <v>7647.09</v>
       </c>
       <c r="AF298">
         <f t="shared" si="17"/>
@@ -29655,7 +29679,7 @@
       </c>
       <c r="AG298" s="4">
         <f t="shared" si="18"/>
-        <v>8606.93</v>
+        <v>7647.09</v>
       </c>
       <c r="AI298" t="s">
         <v>47</v>
@@ -29862,7 +29886,7 @@
       </c>
       <c r="M301" s="4">
         <f t="shared" si="19"/>
-        <v>7046.9399999999987</v>
+        <v>6464.9399999999987</v>
       </c>
       <c r="N301" s="4">
         <v>2302.75</v>
@@ -29871,7 +29895,7 @@
         <v>2797.3199999999997</v>
       </c>
       <c r="P301" s="4">
-        <v>1396.56</v>
+        <v>814.56</v>
       </c>
       <c r="Q301" s="4">
         <v>550.30999999999995</v>
@@ -29896,7 +29920,7 @@
       </c>
       <c r="AE301" s="4">
         <f t="shared" si="20"/>
-        <v>7996.9399999999987</v>
+        <v>7414.9399999999987</v>
       </c>
       <c r="AF301">
         <f t="shared" si="17"/>
@@ -29904,7 +29928,7 @@
       </c>
       <c r="AG301" s="4">
         <f t="shared" si="18"/>
-        <v>7996.9399999999987</v>
+        <v>7414.9399999999987</v>
       </c>
       <c r="AI301" t="s">
         <v>47</v>
@@ -29946,7 +29970,7 @@
       </c>
       <c r="M302" s="4">
         <f t="shared" si="19"/>
-        <v>6356.01</v>
+        <v>6041.7300000000005</v>
       </c>
       <c r="N302" s="4">
         <v>3195.53</v>
@@ -29955,7 +29979,7 @@
         <v>1536.4099999999999</v>
       </c>
       <c r="P302" s="4">
-        <v>1182</v>
+        <v>867.72</v>
       </c>
       <c r="Q302" s="4">
         <v>442.07</v>
@@ -29980,7 +30004,7 @@
       </c>
       <c r="AE302" s="4">
         <f t="shared" si="20"/>
-        <v>7382.01</v>
+        <v>7067.7300000000005</v>
       </c>
       <c r="AF302">
         <f t="shared" si="17"/>
@@ -29988,7 +30012,7 @@
       </c>
       <c r="AG302" s="4">
         <f t="shared" si="18"/>
-        <v>7382.01</v>
+        <v>7067.7300000000005</v>
       </c>
       <c r="AI302" t="s">
         <v>39</v>
@@ -30175,7 +30199,7 @@
       <c r="E305">
         <v>314</v>
       </c>
-      <c r="F305" t="s">
+      <c r="F305" s="8" t="s">
         <v>440</v>
       </c>
       <c r="G305" t="s">
@@ -30195,7 +30219,7 @@
       </c>
       <c r="M305" s="4">
         <f t="shared" si="19"/>
-        <v>9278.1</v>
+        <v>9255.4600000000009</v>
       </c>
       <c r="N305" s="4">
         <v>4681.28</v>
@@ -30204,7 +30228,7 @@
         <v>2736.73</v>
       </c>
       <c r="P305" s="4">
-        <v>669.48</v>
+        <v>646.84</v>
       </c>
       <c r="Q305" s="4">
         <v>1190.6100000000001</v>
@@ -30227,12 +30251,12 @@
       <c r="X305" t="s">
         <v>36</v>
       </c>
-      <c r="Y305">
+      <c r="Y305" s="8">
         <v>14000</v>
       </c>
       <c r="AE305" s="4">
         <f t="shared" si="20"/>
-        <v>10304.1</v>
+        <v>10281.460000000001</v>
       </c>
       <c r="AF305">
         <f t="shared" si="17"/>
@@ -30240,7 +30264,7 @@
       </c>
       <c r="AG305" s="4">
         <f t="shared" si="18"/>
-        <v>24304.1</v>
+        <v>24281.46</v>
       </c>
       <c r="AI305" t="s">
         <v>47</v>
@@ -30340,7 +30364,7 @@
       <c r="E307">
         <v>316</v>
       </c>
-      <c r="F307" t="s">
+      <c r="F307" s="8" t="s">
         <v>641</v>
       </c>
       <c r="G307" t="s">
@@ -30360,7 +30384,7 @@
       </c>
       <c r="M307" s="4">
         <f t="shared" si="19"/>
-        <v>13406.08</v>
+        <v>12794.5</v>
       </c>
       <c r="N307" s="4">
         <v>4681.28</v>
@@ -30369,7 +30393,7 @@
         <v>4634.08</v>
       </c>
       <c r="P307" s="4">
-        <v>2097.1499999999996</v>
+        <v>1485.57</v>
       </c>
       <c r="Q307" s="4">
         <v>1993.5700000000002</v>
@@ -30392,12 +30416,12 @@
       <c r="X307" t="s">
         <v>36</v>
       </c>
-      <c r="Y307">
+      <c r="Y307" s="8">
         <v>15000</v>
       </c>
       <c r="AE307" s="4">
         <f t="shared" si="20"/>
-        <v>14432.08</v>
+        <v>13820.5</v>
       </c>
       <c r="AF307">
         <f t="shared" si="17"/>
@@ -30405,7 +30429,7 @@
       </c>
       <c r="AG307" s="4">
         <f t="shared" si="18"/>
-        <v>29432.080000000002</v>
+        <v>28820.5</v>
       </c>
       <c r="AI307" t="s">
         <v>47</v>
@@ -30609,7 +30633,7 @@
       </c>
       <c r="M310" s="4">
         <f t="shared" si="19"/>
-        <v>6640.4900000000007</v>
+        <v>6142.47</v>
       </c>
       <c r="N310" s="4">
         <v>2801.97</v>
@@ -30618,7 +30642,7 @@
         <v>1819.5300000000002</v>
       </c>
       <c r="P310" s="4">
-        <v>1544.18</v>
+        <v>1046.1600000000001</v>
       </c>
       <c r="Q310" s="4">
         <v>474.81</v>
@@ -30643,7 +30667,7 @@
       </c>
       <c r="AE310" s="4">
         <f t="shared" si="20"/>
-        <v>7704.4900000000007</v>
+        <v>7206.47</v>
       </c>
       <c r="AF310">
         <f t="shared" si="17"/>
@@ -30651,7 +30675,7 @@
       </c>
       <c r="AG310" s="4">
         <f t="shared" si="18"/>
-        <v>7704.4900000000007</v>
+        <v>7206.47</v>
       </c>
       <c r="AI310" t="s">
         <v>47</v>
@@ -30690,7 +30714,7 @@
       </c>
       <c r="M311" s="4">
         <f t="shared" si="19"/>
-        <v>4579.9000000000005</v>
+        <v>4370.3200000000006</v>
       </c>
       <c r="N311" s="4">
         <v>2302.75</v>
@@ -30699,7 +30723,7 @@
         <v>1136.1500000000001</v>
       </c>
       <c r="P311" s="4">
-        <v>836.28</v>
+        <v>626.70000000000005</v>
       </c>
       <c r="Q311" s="4">
         <v>304.72000000000003</v>
@@ -30724,7 +30748,7 @@
       </c>
       <c r="AE311" s="4">
         <f t="shared" si="20"/>
-        <v>5415.9000000000005</v>
+        <v>5206.3200000000006</v>
       </c>
       <c r="AF311">
         <f t="shared" si="17"/>
@@ -30732,7 +30756,7 @@
       </c>
       <c r="AG311" s="4">
         <f t="shared" si="18"/>
-        <v>5415.9000000000005</v>
+        <v>5206.3200000000006</v>
       </c>
       <c r="AI311" t="s">
         <v>47</v>
@@ -30855,7 +30879,7 @@
       </c>
       <c r="M313" s="4">
         <f t="shared" si="19"/>
-        <v>4277.8600000000006</v>
+        <v>3900.1400000000003</v>
       </c>
       <c r="N313" s="4">
         <v>2302.75</v>
@@ -30864,7 +30888,7 @@
         <v>654.0100000000001</v>
       </c>
       <c r="P313" s="4">
-        <v>1051.94</v>
+        <v>674.22</v>
       </c>
       <c r="Q313" s="4">
         <v>269.16000000000003</v>
@@ -30889,7 +30913,7 @@
       </c>
       <c r="AE313" s="4">
         <f t="shared" si="20"/>
-        <v>5189.8600000000006</v>
+        <v>4812.1400000000003</v>
       </c>
       <c r="AF313">
         <f t="shared" si="17"/>
@@ -30897,7 +30921,7 @@
       </c>
       <c r="AG313" s="4">
         <f t="shared" si="18"/>
-        <v>5189.8600000000006</v>
+        <v>4812.1400000000003</v>
       </c>
       <c r="AI313" t="s">
         <v>47</v>
@@ -30936,7 +30960,7 @@
       </c>
       <c r="M314" s="4">
         <f t="shared" si="19"/>
-        <v>6073.7699999999995</v>
+        <v>6041.36</v>
       </c>
       <c r="N314" s="4">
         <v>3356.8</v>
@@ -30945,7 +30969,7 @@
         <v>1624.52</v>
       </c>
       <c r="P314" s="4">
-        <v>616.57000000000005</v>
+        <v>584.16000000000008</v>
       </c>
       <c r="Q314" s="4">
         <v>475.88</v>
@@ -30968,7 +30992,7 @@
       <c r="X314" t="s">
         <v>36</v>
       </c>
-      <c r="Y314">
+      <c r="Y314" s="8">
         <v>10000</v>
       </c>
       <c r="AC314" t="s">
@@ -30979,7 +31003,7 @@
       </c>
       <c r="AE314" s="4">
         <f t="shared" si="20"/>
-        <v>7023.7699999999995</v>
+        <v>6991.36</v>
       </c>
       <c r="AF314">
         <f t="shared" si="17"/>
@@ -30987,7 +31011,7 @@
       </c>
       <c r="AG314" s="4">
         <f t="shared" si="18"/>
-        <v>17023.77</v>
+        <v>16991.36</v>
       </c>
       <c r="AI314" t="s">
         <v>47</v>
@@ -31006,7 +31030,7 @@
       <c r="E315">
         <v>326</v>
       </c>
-      <c r="F315" t="s">
+      <c r="F315" s="9" t="s">
         <v>266</v>
       </c>
       <c r="G315" t="s">
@@ -31061,7 +31085,7 @@
       <c r="X315" t="s">
         <v>36</v>
       </c>
-      <c r="Y315">
+      <c r="Y315" s="8">
         <v>5000</v>
       </c>
       <c r="AE315" s="4">
@@ -31093,7 +31117,7 @@
       <c r="E316">
         <v>327</v>
       </c>
-      <c r="F316" t="s">
+      <c r="F316" s="8" t="s">
         <v>172</v>
       </c>
       <c r="G316" t="s">
@@ -31145,7 +31169,7 @@
       <c r="X316" t="s">
         <v>36</v>
       </c>
-      <c r="Y316">
+      <c r="Y316" s="8">
         <v>15000</v>
       </c>
       <c r="AC316" t="s">
@@ -31287,7 +31311,7 @@
       </c>
       <c r="M318" s="4">
         <f t="shared" si="19"/>
-        <v>4615.68</v>
+        <v>4164.74</v>
       </c>
       <c r="N318" s="4">
         <v>2302.75</v>
@@ -31296,7 +31320,7 @@
         <v>898.4799999999999</v>
       </c>
       <c r="P318" s="4">
-        <v>1119.3599999999999</v>
+        <v>668.42</v>
       </c>
       <c r="Q318" s="4">
         <v>295.08999999999997</v>
@@ -31321,7 +31345,7 @@
       </c>
       <c r="AE318" s="4">
         <f t="shared" si="20"/>
-        <v>5565.68</v>
+        <v>5114.74</v>
       </c>
       <c r="AF318">
         <f t="shared" si="17"/>
@@ -31329,7 +31353,7 @@
       </c>
       <c r="AG318" s="4">
         <f t="shared" si="18"/>
-        <v>5565.68</v>
+        <v>5114.74</v>
       </c>
       <c r="AI318" t="s">
         <v>47</v>
@@ -31348,7 +31372,7 @@
       <c r="E319">
         <v>330</v>
       </c>
-      <c r="F319" t="s">
+      <c r="F319" s="8" t="s">
         <v>376</v>
       </c>
       <c r="G319" t="s">
@@ -31403,7 +31427,7 @@
       <c r="X319" t="s">
         <v>36</v>
       </c>
-      <c r="Y319">
+      <c r="Y319" s="8">
         <v>12000</v>
       </c>
       <c r="AE319" s="4">
@@ -31435,7 +31459,7 @@
       <c r="E320">
         <v>331</v>
       </c>
-      <c r="F320" t="s">
+      <c r="F320" s="8" t="s">
         <v>614</v>
       </c>
       <c r="G320" t="s">
@@ -31491,7 +31515,7 @@
       <c r="X320" t="s">
         <v>36</v>
       </c>
-      <c r="Y320">
+      <c r="Y320" s="8">
         <f>3500+3500</f>
         <v>7000</v>
       </c>
@@ -31524,7 +31548,7 @@
       <c r="E321">
         <v>332</v>
       </c>
-      <c r="F321" t="s">
+      <c r="F321" s="8" t="s">
         <v>639</v>
       </c>
       <c r="G321" t="s">
@@ -31579,7 +31603,7 @@
       <c r="X321" t="s">
         <v>36</v>
       </c>
-      <c r="Y321">
+      <c r="Y321" s="8">
         <v>38000</v>
       </c>
       <c r="AE321" s="4">
@@ -31611,7 +31635,7 @@
       <c r="E322">
         <v>333</v>
       </c>
-      <c r="F322" t="s">
+      <c r="F322" s="8" t="s">
         <v>630</v>
       </c>
       <c r="G322" t="s">
@@ -31663,7 +31687,7 @@
       <c r="X322" t="s">
         <v>36</v>
       </c>
-      <c r="Y322">
+      <c r="Y322" s="8">
         <v>14500</v>
       </c>
       <c r="AE322" s="4">
@@ -31695,7 +31719,7 @@
       <c r="E323">
         <v>334</v>
       </c>
-      <c r="F323" t="s">
+      <c r="F323" s="8" t="s">
         <v>571</v>
       </c>
       <c r="G323" t="s">
@@ -31718,7 +31742,7 @@
       </c>
       <c r="M323" s="4">
         <f t="shared" si="19"/>
-        <v>7424.57</v>
+        <v>6828.57</v>
       </c>
       <c r="N323" s="4">
         <v>3356.8</v>
@@ -31727,7 +31751,7 @@
         <v>2083.7799999999997</v>
       </c>
       <c r="P323" s="4">
-        <v>1444.3200000000002</v>
+        <v>848.32</v>
       </c>
       <c r="Q323" s="4">
         <v>539.66999999999996</v>
@@ -31750,12 +31774,12 @@
       <c r="X323" t="s">
         <v>36</v>
       </c>
-      <c r="Y323">
+      <c r="Y323" s="8">
         <v>15000</v>
       </c>
       <c r="AE323" s="4">
         <f t="shared" si="20"/>
-        <v>8374.57</v>
+        <v>7778.57</v>
       </c>
       <c r="AF323">
         <f t="shared" ref="AF323:AF386" si="21">U323+Y323</f>
@@ -31763,7 +31787,7 @@
       </c>
       <c r="AG323" s="4">
         <f t="shared" ref="AG323:AG386" si="22">AF323+AE323</f>
-        <v>23374.57</v>
+        <v>22778.57</v>
       </c>
       <c r="AI323" t="s">
         <v>47</v>
@@ -31802,7 +31826,7 @@
       </c>
       <c r="M324" s="4">
         <f t="shared" ref="M324:M387" si="23">N324+O324+P324+Q324-S324+R324</f>
-        <v>5204.9399999999996</v>
+        <v>5193.3</v>
       </c>
       <c r="N324" s="4">
         <v>2302.75</v>
@@ -31811,7 +31835,7 @@
         <v>1679.36</v>
       </c>
       <c r="P324" s="4">
-        <v>848.86999999999989</v>
+        <v>837.23</v>
       </c>
       <c r="Q324" s="4">
         <v>373.96</v>
@@ -31836,7 +31860,7 @@
       </c>
       <c r="AE324" s="4">
         <f t="shared" ref="AE324:AE387" si="24">M324+T324+V324</f>
-        <v>6078.94</v>
+        <v>6067.3</v>
       </c>
       <c r="AF324">
         <f t="shared" si="21"/>
@@ -31844,7 +31868,7 @@
       </c>
       <c r="AG324" s="4">
         <f t="shared" si="22"/>
-        <v>6078.94</v>
+        <v>6067.3</v>
       </c>
       <c r="AI324" t="s">
         <v>47</v>
@@ -31863,7 +31887,7 @@
       <c r="E325">
         <v>336</v>
       </c>
-      <c r="F325" t="s">
+      <c r="F325" s="8" t="s">
         <v>425</v>
       </c>
       <c r="G325" t="s">
@@ -31918,7 +31942,7 @@
       <c r="X325" t="s">
         <v>36</v>
       </c>
-      <c r="Y325">
+      <c r="Y325" s="8">
         <v>12000</v>
       </c>
       <c r="AE325" s="4">
@@ -32031,7 +32055,7 @@
       <c r="E327">
         <v>338</v>
       </c>
-      <c r="F327" t="s">
+      <c r="F327" s="8" t="s">
         <v>462</v>
       </c>
       <c r="G327" t="s">
@@ -32083,7 +32107,7 @@
       <c r="X327" t="s">
         <v>36</v>
       </c>
-      <c r="Y327">
+      <c r="Y327" s="8">
         <v>13000</v>
       </c>
       <c r="AE327" s="4">
@@ -32115,7 +32139,7 @@
       <c r="E328">
         <v>339</v>
       </c>
-      <c r="F328" t="s">
+      <c r="F328" s="8" t="s">
         <v>538</v>
       </c>
       <c r="G328" t="s">
@@ -32138,7 +32162,7 @@
       </c>
       <c r="M328" s="4">
         <f t="shared" si="23"/>
-        <v>9847.0400000000009</v>
+        <v>9235.76</v>
       </c>
       <c r="N328" s="4">
         <v>3356.8</v>
@@ -32147,7 +32171,7 @@
         <v>3840.3</v>
       </c>
       <c r="P328" s="4">
-        <v>1481.9799999999998</v>
+        <v>870.7</v>
       </c>
       <c r="Q328" s="4">
         <v>1167.96</v>
@@ -32170,12 +32194,12 @@
       <c r="X328" t="s">
         <v>36</v>
       </c>
-      <c r="Y328">
+      <c r="Y328" s="8">
         <v>38000</v>
       </c>
       <c r="AE328" s="4">
         <f t="shared" si="24"/>
-        <v>10873.04</v>
+        <v>10261.76</v>
       </c>
       <c r="AF328">
         <f t="shared" si="21"/>
@@ -32183,7 +32207,7 @@
       </c>
       <c r="AG328" s="4">
         <f t="shared" si="22"/>
-        <v>48873.04</v>
+        <v>48261.760000000002</v>
       </c>
       <c r="AI328" t="s">
         <v>47</v>
@@ -32393,7 +32417,7 @@
       </c>
       <c r="M331" s="4">
         <f t="shared" si="23"/>
-        <v>5479.34411</v>
+        <v>5331.6641099999997</v>
       </c>
       <c r="N331" s="4">
         <v>2801.9741100000001</v>
@@ -32402,7 +32426,7 @@
         <v>1482.9299999999998</v>
       </c>
       <c r="P331" s="4">
-        <v>886.92000000000007</v>
+        <v>739.24</v>
       </c>
       <c r="Q331" s="4">
         <v>307.52</v>
@@ -32427,7 +32451,7 @@
       </c>
       <c r="AE331" s="4">
         <f t="shared" si="24"/>
-        <v>5479.34411</v>
+        <v>5331.6641099999997</v>
       </c>
       <c r="AF331">
         <f t="shared" si="21"/>
@@ -32435,7 +32459,7 @@
       </c>
       <c r="AG331" s="4">
         <f t="shared" si="22"/>
-        <v>5479.34411</v>
+        <v>5331.6641099999997</v>
       </c>
       <c r="AI331" t="s">
         <v>47</v>
@@ -32474,7 +32498,7 @@
       </c>
       <c r="M332" s="4">
         <f t="shared" si="23"/>
-        <v>6301.0599999999995</v>
+        <v>5582.94</v>
       </c>
       <c r="N332" s="4">
         <v>2302.75</v>
@@ -32483,7 +32507,7 @@
         <v>1814.54</v>
       </c>
       <c r="P332" s="4">
-        <v>1794.08</v>
+        <v>1075.96</v>
       </c>
       <c r="Q332" s="4">
         <v>389.69</v>
@@ -32508,7 +32532,7 @@
       </c>
       <c r="AE332" s="4">
         <f t="shared" si="24"/>
-        <v>7175.0599999999995</v>
+        <v>6456.94</v>
       </c>
       <c r="AF332">
         <f t="shared" si="21"/>
@@ -32516,7 +32540,7 @@
       </c>
       <c r="AG332" s="4">
         <f t="shared" si="22"/>
-        <v>7175.0599999999995</v>
+        <v>6456.94</v>
       </c>
       <c r="AI332" t="s">
         <v>47</v>
@@ -32619,7 +32643,7 @@
       <c r="E334">
         <v>345</v>
       </c>
-      <c r="F334" t="s">
+      <c r="F334" s="8" t="s">
         <v>119</v>
       </c>
       <c r="G334" t="s">
@@ -32671,7 +32695,7 @@
       <c r="X334" t="s">
         <v>36</v>
       </c>
-      <c r="Y334">
+      <c r="Y334" s="8">
         <v>11000</v>
       </c>
       <c r="AE334" s="4">
@@ -32723,7 +32747,7 @@
       </c>
       <c r="M335" s="4">
         <f t="shared" si="23"/>
-        <v>4572.5</v>
+        <v>4524.5599999999995</v>
       </c>
       <c r="N335" s="4">
         <v>2302.75</v>
@@ -32732,7 +32756,7 @@
         <v>1071.82</v>
       </c>
       <c r="P335" s="4">
-        <v>877.1400000000001</v>
+        <v>829.2</v>
       </c>
       <c r="Q335" s="4">
         <v>320.79000000000002</v>
@@ -32757,7 +32781,7 @@
       </c>
       <c r="AE335" s="4">
         <f t="shared" si="24"/>
-        <v>5484.5</v>
+        <v>5436.5599999999995</v>
       </c>
       <c r="AF335">
         <f t="shared" si="21"/>
@@ -32765,7 +32789,7 @@
       </c>
       <c r="AG335" s="4">
         <f t="shared" si="22"/>
-        <v>5484.5</v>
+        <v>5436.5599999999995</v>
       </c>
       <c r="AI335" t="s">
         <v>47</v>
@@ -32807,7 +32831,7 @@
       </c>
       <c r="M336" s="4">
         <f t="shared" si="23"/>
-        <v>6561.37</v>
+        <v>6197.8099999999995</v>
       </c>
       <c r="N336" s="4">
         <v>2801.97</v>
@@ -32816,7 +32840,7 @@
         <v>2021.55</v>
       </c>
       <c r="P336" s="4">
-        <v>1234.3400000000001</v>
+        <v>870.78</v>
       </c>
       <c r="Q336" s="4">
         <v>503.51</v>
@@ -32841,7 +32865,7 @@
       </c>
       <c r="AE336" s="4">
         <f t="shared" si="24"/>
-        <v>7473.37</v>
+        <v>7109.8099999999995</v>
       </c>
       <c r="AF336">
         <f t="shared" si="21"/>
@@ -32849,7 +32873,7 @@
       </c>
       <c r="AG336" s="4">
         <f t="shared" si="22"/>
-        <v>7473.37</v>
+        <v>7109.8099999999995</v>
       </c>
       <c r="AI336" t="s">
         <v>47</v>
@@ -32891,7 +32915,7 @@
       </c>
       <c r="M337" s="4">
         <f t="shared" si="23"/>
-        <v>7140.67</v>
+        <v>6597.3099999999995</v>
       </c>
       <c r="N337" s="4">
         <v>2801.97</v>
@@ -32900,7 +32924,7 @@
         <v>2278.9</v>
       </c>
       <c r="P337" s="4">
-        <v>1522.09</v>
+        <v>978.7299999999999</v>
       </c>
       <c r="Q337" s="4">
         <v>537.71</v>
@@ -32925,7 +32949,7 @@
       </c>
       <c r="AE337" s="4">
         <f t="shared" si="24"/>
-        <v>8052.67</v>
+        <v>7509.3099999999995</v>
       </c>
       <c r="AF337">
         <f t="shared" si="21"/>
@@ -32933,7 +32957,7 @@
       </c>
       <c r="AG337" s="4">
         <f t="shared" si="22"/>
-        <v>8052.67</v>
+        <v>7509.3099999999995</v>
       </c>
       <c r="AI337" t="s">
         <v>47</v>
@@ -32972,7 +32996,7 @@
       </c>
       <c r="M338" s="4">
         <f t="shared" si="23"/>
-        <v>6887.85</v>
+        <v>6544.49</v>
       </c>
       <c r="N338" s="4">
         <v>2801.97</v>
@@ -32981,7 +33005,7 @@
         <v>2334.7000000000003</v>
       </c>
       <c r="P338" s="4">
-        <v>1204.3600000000001</v>
+        <v>861</v>
       </c>
       <c r="Q338" s="4">
         <v>546.82000000000005</v>
@@ -33006,7 +33030,7 @@
       </c>
       <c r="AE338" s="4">
         <f t="shared" si="24"/>
-        <v>7989.85</v>
+        <v>7646.49</v>
       </c>
       <c r="AF338">
         <f t="shared" si="21"/>
@@ -33014,7 +33038,7 @@
       </c>
       <c r="AG338" s="4">
         <f t="shared" si="22"/>
-        <v>7989.85</v>
+        <v>7646.49</v>
       </c>
       <c r="AI338" t="s">
         <v>47</v>
@@ -33053,7 +33077,7 @@
       </c>
       <c r="M339" s="4">
         <f t="shared" si="23"/>
-        <v>5430.0700000000006</v>
+        <v>5102.47</v>
       </c>
       <c r="N339" s="4">
         <v>2302.75</v>
@@ -33062,7 +33086,7 @@
         <v>1773.55</v>
       </c>
       <c r="P339" s="4">
-        <v>950.65000000000009</v>
+        <v>623.05000000000007</v>
       </c>
       <c r="Q339" s="4">
         <v>403.12</v>
@@ -33087,7 +33111,7 @@
       </c>
       <c r="AE339" s="4">
         <f t="shared" si="24"/>
-        <v>6456.0700000000006</v>
+        <v>6128.47</v>
       </c>
       <c r="AF339">
         <f t="shared" si="21"/>
@@ -33095,7 +33119,7 @@
       </c>
       <c r="AG339" s="4">
         <f t="shared" si="22"/>
-        <v>6456.0700000000006</v>
+        <v>6128.47</v>
       </c>
       <c r="AI339" t="s">
         <v>47</v>
@@ -33380,7 +33404,7 @@
       </c>
       <c r="M343" s="4">
         <f t="shared" si="23"/>
-        <v>6262.42</v>
+        <v>5314.9800000000005</v>
       </c>
       <c r="N343" s="4">
         <v>2302.75</v>
@@ -33389,7 +33413,7 @@
         <v>1518.3200000000002</v>
       </c>
       <c r="P343" s="4">
-        <v>2068.8500000000004</v>
+        <v>1121.4100000000001</v>
       </c>
       <c r="Q343" s="4">
         <v>372.5</v>
@@ -33414,7 +33438,7 @@
       </c>
       <c r="AE343" s="4">
         <f t="shared" si="24"/>
-        <v>7250.42</v>
+        <v>6302.9800000000005</v>
       </c>
       <c r="AF343">
         <f t="shared" si="21"/>
@@ -33422,7 +33446,7 @@
       </c>
       <c r="AG343" s="4">
         <f t="shared" si="22"/>
-        <v>7250.42</v>
+        <v>6302.9800000000005</v>
       </c>
       <c r="AI343" t="s">
         <v>47</v>
@@ -33545,7 +33569,7 @@
       </c>
       <c r="M345" s="4">
         <f t="shared" si="23"/>
-        <v>6089.4500000000007</v>
+        <v>5371.77</v>
       </c>
       <c r="N345" s="4">
         <v>2302.75</v>
@@ -33554,7 +33578,7 @@
         <v>1494.22</v>
       </c>
       <c r="P345" s="4">
-        <v>1959.68</v>
+        <v>1242</v>
       </c>
       <c r="Q345" s="4">
         <v>332.8</v>
@@ -33579,7 +33603,7 @@
       </c>
       <c r="AE345" s="4">
         <f t="shared" si="24"/>
-        <v>7001.4500000000007</v>
+        <v>6283.77</v>
       </c>
       <c r="AF345">
         <f t="shared" si="21"/>
@@ -33587,7 +33611,7 @@
       </c>
       <c r="AG345" s="4">
         <f t="shared" si="22"/>
-        <v>7001.4500000000007</v>
+        <v>6283.77</v>
       </c>
       <c r="AI345" t="s">
         <v>47</v>
@@ -33707,7 +33731,7 @@
       </c>
       <c r="M347" s="4">
         <f t="shared" si="23"/>
-        <v>3617.89</v>
+        <v>3606.25</v>
       </c>
       <c r="N347" s="4">
         <v>2302.75</v>
@@ -33716,7 +33740,7 @@
         <v>613.08000000000004</v>
       </c>
       <c r="P347" s="4">
-        <v>497.48</v>
+        <v>485.84</v>
       </c>
       <c r="Q347" s="4">
         <v>204.58</v>
@@ -33741,7 +33765,7 @@
       </c>
       <c r="AE347" s="4">
         <f t="shared" si="24"/>
-        <v>4491.8899999999994</v>
+        <v>4480.25</v>
       </c>
       <c r="AF347">
         <f t="shared" si="21"/>
@@ -33749,7 +33773,7 @@
       </c>
       <c r="AG347" s="4">
         <f t="shared" si="22"/>
-        <v>4491.8899999999994</v>
+        <v>4480.25</v>
       </c>
       <c r="AI347" t="s">
         <v>47</v>
@@ -33869,7 +33893,7 @@
       </c>
       <c r="M349" s="4">
         <f t="shared" si="23"/>
-        <v>5292.8899999999994</v>
+        <v>4827.29</v>
       </c>
       <c r="N349" s="4">
         <v>2302.75</v>
@@ -33878,7 +33902,7 @@
         <v>1476.6499999999999</v>
       </c>
       <c r="P349" s="4">
-        <v>1146.2</v>
+        <v>680.6</v>
       </c>
       <c r="Q349" s="4">
         <v>367.29</v>
@@ -33903,7 +33927,7 @@
       </c>
       <c r="AE349" s="4">
         <f t="shared" si="24"/>
-        <v>6204.8899999999994</v>
+        <v>5739.29</v>
       </c>
       <c r="AF349">
         <f t="shared" si="21"/>
@@ -33911,7 +33935,7 @@
       </c>
       <c r="AG349" s="4">
         <f t="shared" si="22"/>
-        <v>6204.8899999999994</v>
+        <v>5739.29</v>
       </c>
       <c r="AI349" t="s">
         <v>47</v>
@@ -33930,7 +33954,7 @@
       <c r="E350">
         <v>363</v>
       </c>
-      <c r="F350" t="s">
+      <c r="F350" s="8" t="s">
         <v>625</v>
       </c>
       <c r="G350" t="s">
@@ -33982,7 +34006,7 @@
       <c r="X350" t="s">
         <v>36</v>
       </c>
-      <c r="Y350">
+      <c r="Y350" s="8">
         <v>15000</v>
       </c>
       <c r="AE350" s="4">
@@ -34095,7 +34119,7 @@
       <c r="E352">
         <v>365</v>
       </c>
-      <c r="F352" t="s">
+      <c r="F352" s="8" t="s">
         <v>421</v>
       </c>
       <c r="G352" t="s">
@@ -34147,7 +34171,7 @@
       <c r="X352" t="s">
         <v>36</v>
       </c>
-      <c r="Y352">
+      <c r="Y352" s="8">
         <f>33500+15000</f>
         <v>48500</v>
       </c>
@@ -34200,7 +34224,7 @@
       </c>
       <c r="M353" s="4">
         <f t="shared" si="23"/>
-        <v>5689.8700000000008</v>
+        <v>5422.15</v>
       </c>
       <c r="N353" s="4">
         <v>2302.75</v>
@@ -34209,7 +34233,7 @@
         <v>2033.05</v>
       </c>
       <c r="P353" s="4">
-        <v>923.2700000000001</v>
+        <v>655.55000000000007</v>
       </c>
       <c r="Q353" s="4">
         <v>430.8</v>
@@ -34234,7 +34258,7 @@
       </c>
       <c r="AE353" s="4">
         <f t="shared" si="24"/>
-        <v>6563.8700000000008</v>
+        <v>6296.15</v>
       </c>
       <c r="AF353">
         <f t="shared" si="21"/>
@@ -34242,7 +34266,7 @@
       </c>
       <c r="AG353" s="4">
         <f t="shared" si="22"/>
-        <v>6563.8700000000008</v>
+        <v>6296.15</v>
       </c>
       <c r="AI353" t="s">
         <v>47</v>
@@ -34281,7 +34305,7 @@
       </c>
       <c r="M354" s="4">
         <f t="shared" si="23"/>
-        <v>5772.2</v>
+        <v>5235.72</v>
       </c>
       <c r="N354" s="4">
         <v>2801.97</v>
@@ -34290,7 +34314,7 @@
         <v>1567.0099999999998</v>
       </c>
       <c r="P354" s="4">
-        <v>1006.41</v>
+        <v>469.93</v>
       </c>
       <c r="Q354" s="4">
         <v>396.81</v>
@@ -34315,7 +34339,7 @@
       </c>
       <c r="AE354" s="4">
         <f t="shared" si="24"/>
-        <v>6646.2</v>
+        <v>6109.72</v>
       </c>
       <c r="AF354">
         <f t="shared" si="21"/>
@@ -34323,7 +34347,7 @@
       </c>
       <c r="AG354" s="4">
         <f t="shared" si="22"/>
-        <v>6646.2</v>
+        <v>6109.72</v>
       </c>
       <c r="AI354" t="s">
         <v>47</v>
@@ -34362,7 +34386,7 @@
       </c>
       <c r="M355" s="4">
         <f t="shared" si="23"/>
-        <v>4843.3900000000003</v>
+        <v>4582.75</v>
       </c>
       <c r="N355" s="4">
         <v>2302.75</v>
@@ -34371,7 +34395,7 @@
         <v>1176.97</v>
       </c>
       <c r="P355" s="4">
-        <v>1049.58</v>
+        <v>788.94</v>
       </c>
       <c r="Q355" s="4">
         <v>314.08999999999997</v>
@@ -34396,7 +34420,7 @@
       </c>
       <c r="AE355" s="4">
         <f t="shared" si="24"/>
-        <v>5641.39</v>
+        <v>5380.75</v>
       </c>
       <c r="AF355">
         <f t="shared" si="21"/>
@@ -34404,7 +34428,7 @@
       </c>
       <c r="AG355" s="4">
         <f t="shared" si="22"/>
-        <v>5641.39</v>
+        <v>5380.75</v>
       </c>
       <c r="AI355" t="s">
         <v>47</v>
@@ -34443,7 +34467,7 @@
       </c>
       <c r="M356" s="4">
         <f t="shared" si="23"/>
-        <v>5390.7200000000012</v>
+        <v>4870</v>
       </c>
       <c r="N356" s="4">
         <v>2302.75</v>
@@ -34452,7 +34476,7 @@
         <v>1365.04</v>
       </c>
       <c r="P356" s="4">
-        <v>1393.54</v>
+        <v>872.81999999999994</v>
       </c>
       <c r="Q356" s="4">
         <v>329.39</v>
@@ -34477,7 +34501,7 @@
       </c>
       <c r="AE356" s="4">
         <f t="shared" si="24"/>
-        <v>6264.7200000000012</v>
+        <v>5744</v>
       </c>
       <c r="AF356">
         <f t="shared" si="21"/>
@@ -34485,7 +34509,7 @@
       </c>
       <c r="AG356" s="4">
         <f t="shared" si="22"/>
-        <v>6264.7200000000012</v>
+        <v>5744</v>
       </c>
       <c r="AI356" t="s">
         <v>47</v>
@@ -34524,7 +34548,7 @@
       </c>
       <c r="M357" s="4">
         <f t="shared" si="23"/>
-        <v>4921.34</v>
+        <v>4546.62</v>
       </c>
       <c r="N357" s="4">
         <v>2302.75</v>
@@ -34533,7 +34557,7 @@
         <v>1259.49</v>
       </c>
       <c r="P357" s="4">
-        <v>1039.96</v>
+        <v>665.24</v>
       </c>
       <c r="Q357" s="4">
         <v>319.14</v>
@@ -34558,7 +34582,7 @@
       </c>
       <c r="AE357" s="4">
         <f t="shared" si="24"/>
-        <v>5909.34</v>
+        <v>5534.62</v>
       </c>
       <c r="AF357">
         <f t="shared" si="21"/>
@@ -34566,7 +34590,7 @@
       </c>
       <c r="AG357" s="4">
         <f t="shared" si="22"/>
-        <v>5909.34</v>
+        <v>5534.62</v>
       </c>
       <c r="AI357" t="s">
         <v>47</v>
@@ -34605,7 +34629,7 @@
       </c>
       <c r="M358" s="4">
         <f t="shared" si="23"/>
-        <v>3935.95</v>
+        <v>3492.4300000000003</v>
       </c>
       <c r="N358" s="4">
         <v>2302.75</v>
@@ -34614,7 +34638,7 @@
         <v>537.19000000000005</v>
       </c>
       <c r="P358" s="4">
-        <v>916.52</v>
+        <v>473.00000000000006</v>
       </c>
       <c r="Q358" s="4">
         <v>179.49</v>
@@ -34639,7 +34663,7 @@
       </c>
       <c r="AE358" s="4">
         <f t="shared" si="24"/>
-        <v>4619.95</v>
+        <v>4176.43</v>
       </c>
       <c r="AF358">
         <f t="shared" si="21"/>
@@ -34647,7 +34671,7 @@
       </c>
       <c r="AG358" s="4">
         <f t="shared" si="22"/>
-        <v>4619.95</v>
+        <v>4176.43</v>
       </c>
       <c r="AI358" t="s">
         <v>47</v>
@@ -35173,7 +35197,7 @@
       <c r="E365">
         <v>378</v>
       </c>
-      <c r="F365" t="s">
+      <c r="F365" s="8" t="s">
         <v>526</v>
       </c>
       <c r="G365" t="s">
@@ -35193,7 +35217,7 @@
       </c>
       <c r="M365" s="4">
         <f t="shared" si="23"/>
-        <v>8913.9699999999993</v>
+        <v>8073.0100000000011</v>
       </c>
       <c r="N365" s="4">
         <v>4416.3</v>
@@ -35202,7 +35226,7 @@
         <v>1735.4</v>
       </c>
       <c r="P365" s="4">
-        <v>2128.6400000000003</v>
+        <v>1287.68</v>
       </c>
       <c r="Q365" s="4">
         <v>633.63</v>
@@ -35225,12 +35249,12 @@
       <c r="X365" t="s">
         <v>36</v>
       </c>
-      <c r="Y365">
+      <c r="Y365" s="8">
         <v>25000</v>
       </c>
       <c r="AE365" s="4">
         <f t="shared" si="24"/>
-        <v>9825.9699999999993</v>
+        <v>8985.010000000002</v>
       </c>
       <c r="AF365">
         <f t="shared" si="21"/>
@@ -35238,7 +35262,7 @@
       </c>
       <c r="AG365" s="4">
         <f t="shared" si="22"/>
-        <v>34825.97</v>
+        <v>33985.01</v>
       </c>
       <c r="AI365" t="s">
         <v>47</v>
@@ -35277,7 +35301,7 @@
       </c>
       <c r="M366" s="4">
         <f t="shared" si="23"/>
-        <v>3335.05</v>
+        <v>3160.45</v>
       </c>
       <c r="N366" s="4">
         <v>2302.75</v>
@@ -35286,7 +35310,7 @@
         <v>202.66</v>
       </c>
       <c r="P366" s="4">
-        <v>673.4</v>
+        <v>498.79999999999995</v>
       </c>
       <c r="Q366" s="4">
         <v>156.24</v>
@@ -35311,7 +35335,7 @@
       </c>
       <c r="AE366" s="4">
         <f t="shared" si="24"/>
-        <v>4171.05</v>
+        <v>3996.45</v>
       </c>
       <c r="AF366">
         <f t="shared" si="21"/>
@@ -35319,7 +35343,7 @@
       </c>
       <c r="AG366" s="4">
         <f t="shared" si="22"/>
-        <v>4171.05</v>
+        <v>3996.45</v>
       </c>
       <c r="AI366" t="s">
         <v>47</v>
@@ -35358,7 +35382,7 @@
       </c>
       <c r="M367" s="4">
         <f t="shared" si="23"/>
-        <v>3793.73</v>
+        <v>3279.53</v>
       </c>
       <c r="N367" s="4">
         <v>2302.75</v>
@@ -35367,7 +35391,7 @@
         <v>0</v>
       </c>
       <c r="P367" s="4">
-        <v>1352.6</v>
+        <v>838.40000000000009</v>
       </c>
       <c r="Q367" s="4">
         <v>138.38</v>
@@ -35392,7 +35416,7 @@
       </c>
       <c r="AE367" s="4">
         <f t="shared" si="24"/>
-        <v>4629.7299999999996</v>
+        <v>4115.5300000000007</v>
       </c>
       <c r="AF367">
         <f t="shared" si="21"/>
@@ -35400,7 +35424,7 @@
       </c>
       <c r="AG367" s="4">
         <f t="shared" si="22"/>
-        <v>4629.7299999999996</v>
+        <v>4115.5300000000007</v>
       </c>
       <c r="AI367" t="s">
         <v>47</v>
@@ -35439,7 +35463,7 @@
       </c>
       <c r="M368" s="4">
         <f t="shared" si="23"/>
-        <v>3629.52</v>
+        <v>3280.32</v>
       </c>
       <c r="N368" s="4">
         <v>2302.75</v>
@@ -35448,7 +35472,7 @@
         <v>152.1</v>
       </c>
       <c r="P368" s="4">
-        <v>1022.5999999999999</v>
+        <v>673.4</v>
       </c>
       <c r="Q368" s="4">
         <v>152.07</v>
@@ -35473,7 +35497,7 @@
       </c>
       <c r="AE368" s="4">
         <f t="shared" si="24"/>
-        <v>3629.52</v>
+        <v>3280.32</v>
       </c>
       <c r="AF368">
         <f t="shared" si="21"/>
@@ -35481,7 +35505,7 @@
       </c>
       <c r="AG368" s="4">
         <f t="shared" si="22"/>
-        <v>3629.52</v>
+        <v>3280.32</v>
       </c>
       <c r="AI368" t="s">
         <v>47</v>
@@ -35520,7 +35544,7 @@
       </c>
       <c r="M369" s="4">
         <f t="shared" si="23"/>
-        <v>3612.3134550000004</v>
+        <v>3114.233455</v>
       </c>
       <c r="N369" s="4">
         <v>2302.753455</v>
@@ -35529,7 +35553,7 @@
         <v>8.5299999999999994</v>
       </c>
       <c r="P369" s="4">
-        <v>1161.8800000000001</v>
+        <v>663.8</v>
       </c>
       <c r="Q369" s="4">
         <v>139.15</v>
@@ -35554,7 +35578,7 @@
       </c>
       <c r="AE369" s="4">
         <f t="shared" si="24"/>
-        <v>4448.3134550000004</v>
+        <v>3950.233455</v>
       </c>
       <c r="AF369">
         <f t="shared" si="21"/>
@@ -35562,7 +35586,7 @@
       </c>
       <c r="AG369" s="4">
         <f t="shared" si="22"/>
-        <v>4448.3134550000004</v>
+        <v>3950.233455</v>
       </c>
       <c r="AI369" t="s">
         <v>47</v>
@@ -35601,7 +35625,7 @@
       </c>
       <c r="M370" s="4">
         <f t="shared" si="23"/>
-        <v>3658.61</v>
+        <v>3398.1299999999997</v>
       </c>
       <c r="N370" s="4">
         <v>2302.75</v>
@@ -35610,7 +35634,7 @@
         <v>183.03</v>
       </c>
       <c r="P370" s="4">
-        <v>1018.3599999999999</v>
+        <v>757.87999999999988</v>
       </c>
       <c r="Q370" s="4">
         <v>154.47</v>
@@ -35635,7 +35659,7 @@
       </c>
       <c r="AE370" s="4">
         <f t="shared" si="24"/>
-        <v>4494.6100000000006</v>
+        <v>4234.1299999999992</v>
       </c>
       <c r="AF370">
         <f t="shared" si="21"/>
@@ -35643,7 +35667,7 @@
       </c>
       <c r="AG370" s="4">
         <f t="shared" si="22"/>
-        <v>4494.6100000000006</v>
+        <v>4234.1299999999992</v>
       </c>
       <c r="AI370" t="s">
         <v>47</v>
@@ -35682,7 +35706,7 @@
       </c>
       <c r="M371" s="4">
         <f t="shared" si="23"/>
-        <v>3864.0299999999997</v>
+        <v>3109.87</v>
       </c>
       <c r="N371" s="4">
         <v>2302.75</v>
@@ -35691,7 +35715,7 @@
         <v>168.54000000000002</v>
       </c>
       <c r="P371" s="4">
-        <v>1268.3599999999999</v>
+        <v>514.20000000000005</v>
       </c>
       <c r="Q371" s="4">
         <v>124.38</v>
@@ -35716,7 +35740,7 @@
       </c>
       <c r="AE371" s="4">
         <f t="shared" si="24"/>
-        <v>4700.03</v>
+        <v>3945.87</v>
       </c>
       <c r="AF371">
         <f t="shared" si="21"/>
@@ -35724,7 +35748,7 @@
       </c>
       <c r="AG371" s="4">
         <f t="shared" si="22"/>
-        <v>4700.03</v>
+        <v>3945.87</v>
       </c>
       <c r="AI371" t="s">
         <v>47</v>
@@ -35763,7 +35787,7 @@
       </c>
       <c r="M372" s="4">
         <f t="shared" si="23"/>
-        <v>3333.03</v>
+        <v>3158.43</v>
       </c>
       <c r="N372" s="4">
         <v>2302.75</v>
@@ -35772,7 +35796,7 @@
         <v>200.53</v>
       </c>
       <c r="P372" s="4">
-        <v>673.4</v>
+        <v>498.79999999999995</v>
       </c>
       <c r="Q372" s="4">
         <v>156.35</v>
@@ -35797,7 +35821,7 @@
       </c>
       <c r="AE372" s="4">
         <f t="shared" si="24"/>
-        <v>3333.03</v>
+        <v>3158.43</v>
       </c>
       <c r="AF372">
         <f t="shared" si="21"/>
@@ -35805,7 +35829,7 @@
       </c>
       <c r="AG372" s="4">
         <f t="shared" si="22"/>
-        <v>3333.03</v>
+        <v>3158.43</v>
       </c>
       <c r="AI372" t="s">
         <v>47</v>
@@ -35844,7 +35868,7 @@
       </c>
       <c r="M373" s="4">
         <f t="shared" si="23"/>
-        <v>3221.56</v>
+        <v>3005.56</v>
       </c>
       <c r="N373" s="4">
         <v>2302.75</v>
@@ -35853,7 +35877,7 @@
         <v>55.25</v>
       </c>
       <c r="P373" s="4">
-        <v>720.2</v>
+        <v>504.2</v>
       </c>
       <c r="Q373" s="4">
         <v>143.36000000000001</v>
@@ -35878,7 +35902,7 @@
       </c>
       <c r="AE373" s="4">
         <f t="shared" si="24"/>
-        <v>4057.56</v>
+        <v>3841.56</v>
       </c>
       <c r="AF373">
         <f t="shared" si="21"/>
@@ -35886,7 +35910,7 @@
       </c>
       <c r="AG373" s="4">
         <f t="shared" si="22"/>
-        <v>4057.56</v>
+        <v>3841.56</v>
       </c>
       <c r="AI373" t="s">
         <v>47</v>
@@ -36006,7 +36030,7 @@
       </c>
       <c r="M375" s="4">
         <f t="shared" si="23"/>
-        <v>3356.8500000000004</v>
+        <v>3158.9700000000003</v>
       </c>
       <c r="N375" s="4">
         <v>2302.75</v>
@@ -36015,7 +36039,7 @@
         <v>200.95000000000002</v>
       </c>
       <c r="P375" s="4">
-        <v>696.68000000000006</v>
+        <v>498.79999999999995</v>
       </c>
       <c r="Q375" s="4">
         <v>156.47</v>
@@ -36040,7 +36064,7 @@
       </c>
       <c r="AE375" s="4">
         <f t="shared" si="24"/>
-        <v>4192.8500000000004</v>
+        <v>3994.9700000000003</v>
       </c>
       <c r="AF375">
         <f t="shared" si="21"/>
@@ -36048,7 +36072,7 @@
       </c>
       <c r="AG375" s="4">
         <f t="shared" si="22"/>
-        <v>4192.8500000000004</v>
+        <v>3994.9700000000003</v>
       </c>
       <c r="AI375" t="s">
         <v>47</v>
@@ -36087,7 +36111,7 @@
       </c>
       <c r="M376" s="4">
         <f t="shared" si="23"/>
-        <v>3258.62</v>
+        <v>2994.6199999999994</v>
       </c>
       <c r="N376" s="4">
         <v>2302.75</v>
@@ -36096,7 +36120,7 @@
         <v>45.22</v>
       </c>
       <c r="P376" s="4">
-        <v>768.2</v>
+        <v>504.2</v>
       </c>
       <c r="Q376" s="4">
         <v>142.44999999999999</v>
@@ -36121,7 +36145,7 @@
       </c>
       <c r="AE376" s="4">
         <f t="shared" si="24"/>
-        <v>4094.62</v>
+        <v>3830.6199999999994</v>
       </c>
       <c r="AF376">
         <f t="shared" si="21"/>
@@ -36129,7 +36153,7 @@
       </c>
       <c r="AG376" s="4">
         <f t="shared" si="22"/>
-        <v>4094.62</v>
+        <v>3830.6199999999994</v>
       </c>
       <c r="AI376" t="s">
         <v>47</v>
@@ -36168,7 +36192,7 @@
       </c>
       <c r="M377" s="4">
         <f t="shared" si="23"/>
-        <v>4144.3141100000003</v>
+        <v>3679.0341100000001</v>
       </c>
       <c r="N377" s="4">
         <v>2801.9741100000001</v>
@@ -36177,7 +36201,7 @@
         <v>25.62</v>
       </c>
       <c r="P377" s="4">
-        <v>1147.08</v>
+        <v>681.8</v>
       </c>
       <c r="Q377" s="4">
         <v>169.64</v>
@@ -36202,7 +36226,7 @@
       </c>
       <c r="AE377" s="4">
         <f t="shared" si="24"/>
-        <v>4144.3141100000003</v>
+        <v>3679.0341100000001</v>
       </c>
       <c r="AF377">
         <f t="shared" si="21"/>
@@ -36210,7 +36234,7 @@
       </c>
       <c r="AG377" s="4">
         <f t="shared" si="22"/>
-        <v>4144.3141100000003</v>
+        <v>3679.0341100000001</v>
       </c>
       <c r="AI377" t="s">
         <v>47</v>
@@ -36249,7 +36273,7 @@
       </c>
       <c r="M378" s="4">
         <f t="shared" si="23"/>
-        <v>4284.47</v>
+        <v>3680.87</v>
       </c>
       <c r="N378" s="4">
         <v>2302.75</v>
@@ -36258,7 +36282,7 @@
         <v>349</v>
       </c>
       <c r="P378" s="4">
-        <v>1461.64</v>
+        <v>858.04</v>
       </c>
       <c r="Q378" s="4">
         <v>171.08</v>
@@ -36283,7 +36307,7 @@
       </c>
       <c r="AE378" s="4">
         <f t="shared" si="24"/>
-        <v>5120.47</v>
+        <v>4516.87</v>
       </c>
       <c r="AF378">
         <f t="shared" si="21"/>
@@ -36291,7 +36315,7 @@
       </c>
       <c r="AG378" s="4">
         <f t="shared" si="22"/>
-        <v>5120.47</v>
+        <v>4516.87</v>
       </c>
       <c r="AI378" t="s">
         <v>47</v>
@@ -36310,7 +36334,7 @@
       <c r="E379">
         <v>392</v>
       </c>
-      <c r="F379" t="s">
+      <c r="F379" s="8" t="s">
         <v>671</v>
       </c>
       <c r="G379" t="s">
@@ -36330,7 +36354,7 @@
       </c>
       <c r="M379" s="4">
         <f t="shared" si="23"/>
-        <v>4725.1600000000008</v>
+        <v>4283.5600000000004</v>
       </c>
       <c r="N379" s="4">
         <v>3356.8</v>
@@ -36339,7 +36363,7 @@
         <v>41.78</v>
       </c>
       <c r="P379" s="4">
-        <v>1123.4000000000001</v>
+        <v>681.8</v>
       </c>
       <c r="Q379" s="4">
         <v>203.18</v>
@@ -36362,12 +36386,12 @@
       <c r="X379" t="s">
         <v>36</v>
       </c>
-      <c r="Y379">
+      <c r="Y379" s="8">
         <v>14000</v>
       </c>
       <c r="AE379" s="4">
         <f t="shared" si="24"/>
-        <v>5295.1600000000008</v>
+        <v>4853.5600000000004</v>
       </c>
       <c r="AF379">
         <f t="shared" si="21"/>
@@ -36375,7 +36399,7 @@
       </c>
       <c r="AG379" s="4">
         <f t="shared" si="22"/>
-        <v>19295.16</v>
+        <v>18853.560000000001</v>
       </c>
       <c r="AI379" t="s">
         <v>47</v>
@@ -36414,7 +36438,7 @@
       </c>
       <c r="M380" s="4">
         <f t="shared" si="23"/>
-        <v>3684.38</v>
+        <v>3420.38</v>
       </c>
       <c r="N380" s="4">
         <v>2302.75</v>
@@ -36423,7 +36447,7 @@
         <v>200.95000000000002</v>
       </c>
       <c r="P380" s="4">
-        <v>1024.28</v>
+        <v>760.28</v>
       </c>
       <c r="Q380" s="4">
         <v>156.4</v>
@@ -36448,7 +36472,7 @@
       </c>
       <c r="AE380" s="4">
         <f t="shared" si="24"/>
-        <v>4520.38</v>
+        <v>4256.38</v>
       </c>
       <c r="AF380">
         <f t="shared" si="21"/>
@@ -36456,7 +36480,7 @@
       </c>
       <c r="AG380" s="4">
         <f t="shared" si="22"/>
-        <v>4520.38</v>
+        <v>4256.38</v>
       </c>
       <c r="AI380" t="s">
         <v>47</v>
@@ -36495,7 +36519,7 @@
       </c>
       <c r="M381" s="4">
         <f t="shared" si="23"/>
-        <v>4400.3</v>
+        <v>3924.8599999999997</v>
       </c>
       <c r="N381" s="4">
         <v>2801.97</v>
@@ -36504,7 +36528,7 @@
         <v>106.52</v>
       </c>
       <c r="P381" s="4">
-        <v>1330.88</v>
+        <v>855.44</v>
       </c>
       <c r="Q381" s="4">
         <v>160.93</v>
@@ -36529,7 +36553,7 @@
       </c>
       <c r="AE381" s="4">
         <f t="shared" si="24"/>
-        <v>5198.3</v>
+        <v>4722.8599999999997</v>
       </c>
       <c r="AF381">
         <f t="shared" si="21"/>
@@ -36537,7 +36561,7 @@
       </c>
       <c r="AG381" s="4">
         <f t="shared" si="22"/>
-        <v>5198.3</v>
+        <v>4722.8599999999997</v>
       </c>
       <c r="AI381" t="s">
         <v>47</v>
@@ -36576,7 +36600,7 @@
       </c>
       <c r="M382" s="4">
         <f t="shared" si="23"/>
-        <v>3924.37</v>
+        <v>3726.49</v>
       </c>
       <c r="N382" s="4">
         <v>2801.97</v>
@@ -36585,7 +36609,7 @@
         <v>237.13</v>
       </c>
       <c r="P382" s="4">
-        <v>696.68000000000006</v>
+        <v>498.79999999999995</v>
       </c>
       <c r="Q382" s="4">
         <v>188.59</v>
@@ -36610,7 +36634,7 @@
       </c>
       <c r="AE382" s="4">
         <f t="shared" si="24"/>
-        <v>4760.37</v>
+        <v>4562.49</v>
       </c>
       <c r="AF382">
         <f t="shared" si="21"/>
@@ -36618,7 +36642,7 @@
       </c>
       <c r="AG382" s="4">
         <f t="shared" si="22"/>
-        <v>4760.37</v>
+        <v>4562.49</v>
       </c>
       <c r="AI382" t="s">
         <v>47</v>
@@ -36657,7 +36681,7 @@
       </c>
       <c r="M383" s="4">
         <f t="shared" si="23"/>
-        <v>3801.3</v>
+        <v>3276.82</v>
       </c>
       <c r="N383" s="4">
         <v>2302.75</v>
@@ -36666,7 +36690,7 @@
         <v>140.36000000000001</v>
       </c>
       <c r="P383" s="4">
-        <v>1207.0999999999999</v>
+        <v>682.62</v>
       </c>
       <c r="Q383" s="4">
         <v>151.09</v>
@@ -36691,7 +36715,7 @@
       </c>
       <c r="AE383" s="4">
         <f t="shared" si="24"/>
-        <v>4637.3</v>
+        <v>4112.82</v>
       </c>
       <c r="AF383">
         <f t="shared" si="21"/>
@@ -36699,7 +36723,7 @@
       </c>
       <c r="AG383" s="4">
         <f t="shared" si="22"/>
-        <v>4637.3</v>
+        <v>4112.82</v>
       </c>
       <c r="AI383" t="s">
         <v>47</v>
@@ -36738,7 +36762,7 @@
       </c>
       <c r="M384" s="4">
         <f t="shared" si="23"/>
-        <v>4033.7599999999998</v>
+        <v>3859.16</v>
       </c>
       <c r="N384" s="4">
         <v>2801.97</v>
@@ -36747,7 +36771,7 @@
         <v>358.84999999999997</v>
       </c>
       <c r="P384" s="4">
-        <v>673.4</v>
+        <v>498.79999999999995</v>
       </c>
       <c r="Q384" s="4">
         <v>199.54</v>
@@ -36772,7 +36796,7 @@
       </c>
       <c r="AE384" s="4">
         <f t="shared" si="24"/>
-        <v>4869.76</v>
+        <v>4695.16</v>
       </c>
       <c r="AF384">
         <f t="shared" si="21"/>
@@ -36780,7 +36804,7 @@
       </c>
       <c r="AG384" s="4">
         <f t="shared" si="22"/>
-        <v>4869.76</v>
+        <v>4695.16</v>
       </c>
       <c r="AI384" t="s">
         <v>47</v>
@@ -36819,7 +36843,7 @@
       </c>
       <c r="M385" s="4">
         <f t="shared" si="23"/>
-        <v>4309.9299999999994</v>
+        <v>3555.93</v>
       </c>
       <c r="N385" s="4">
         <v>2819.39</v>
@@ -36828,7 +36852,7 @@
         <v>24.57</v>
       </c>
       <c r="P385" s="4">
-        <v>1324.6</v>
+        <v>570.6</v>
       </c>
       <c r="Q385" s="4">
         <v>141.37</v>
@@ -36853,7 +36877,7 @@
       </c>
       <c r="AE385" s="4">
         <f t="shared" si="24"/>
-        <v>5145.9299999999994</v>
+        <v>4391.93</v>
       </c>
       <c r="AF385">
         <f t="shared" si="21"/>
@@ -36861,7 +36885,7 @@
       </c>
       <c r="AG385" s="4">
         <f t="shared" si="22"/>
-        <v>5145.9299999999994</v>
+        <v>4391.93</v>
       </c>
       <c r="AI385" t="s">
         <v>47</v>
@@ -36961,7 +36985,7 @@
       <c r="E387">
         <v>401</v>
       </c>
-      <c r="F387" t="s">
+      <c r="F387" s="8" t="s">
         <v>676</v>
       </c>
       <c r="G387" t="s">
@@ -37013,7 +37037,7 @@
       <c r="X387" t="s">
         <v>36</v>
       </c>
-      <c r="Y387">
+      <c r="Y387" s="8">
         <v>9000</v>
       </c>
       <c r="AE387" s="4">
@@ -37126,7 +37150,7 @@
       <c r="E389">
         <v>403</v>
       </c>
-      <c r="F389" t="s">
+      <c r="F389" s="8" t="s">
         <v>690</v>
       </c>
       <c r="G389" t="s">
@@ -37178,7 +37202,7 @@
       <c r="X389" t="s">
         <v>36</v>
       </c>
-      <c r="Y389">
+      <c r="Y389" s="8">
         <v>14000</v>
       </c>
       <c r="AE389" s="4">
@@ -37210,7 +37234,7 @@
       <c r="E390">
         <v>404</v>
       </c>
-      <c r="F390" t="s">
+      <c r="F390" s="8" t="s">
         <v>681</v>
       </c>
       <c r="G390" t="s">
@@ -37262,7 +37286,7 @@
       <c r="X390" t="s">
         <v>36</v>
       </c>
-      <c r="Y390">
+      <c r="Y390" s="8">
         <v>38000</v>
       </c>
       <c r="AE390" s="4">
@@ -37945,7 +37969,7 @@
       <c r="E399">
         <v>414</v>
       </c>
-      <c r="F399" t="s">
+      <c r="F399" s="8" t="s">
         <v>700</v>
       </c>
       <c r="G399" t="s">
@@ -37997,7 +38021,7 @@
       <c r="X399" t="s">
         <v>36</v>
       </c>
-      <c r="Y399">
+      <c r="Y399" s="8">
         <v>15000</v>
       </c>
       <c r="AE399" s="4">
@@ -38353,7 +38377,7 @@
       <c r="E404">
         <v>419</v>
       </c>
-      <c r="F404" t="s">
+      <c r="F404" s="8" t="s">
         <v>696</v>
       </c>
       <c r="G404" t="s">
@@ -38405,7 +38429,7 @@
       <c r="X404" t="s">
         <v>36</v>
       </c>
-      <c r="Y404">
+      <c r="Y404" s="8">
         <v>38000</v>
       </c>
       <c r="AE404" s="4">
@@ -38437,7 +38461,7 @@
       <c r="E405">
         <v>420</v>
       </c>
-      <c r="F405" t="s">
+      <c r="F405" s="8" t="s">
         <v>697</v>
       </c>
       <c r="G405" t="s">
@@ -38489,7 +38513,7 @@
       <c r="X405" t="s">
         <v>36</v>
       </c>
-      <c r="Y405">
+      <c r="Y405" s="8">
         <v>15000</v>
       </c>
       <c r="AE405" s="4">
@@ -40400,8 +40424,8 @@
       <c r="D426" t="s">
         <v>73</v>
       </c>
-      <c r="E426" t="s">
-        <v>752</v>
+      <c r="E426">
+        <v>5021</v>
       </c>
       <c r="F426" t="s">
         <v>357</v>
@@ -40703,13 +40727,13 @@
       <c r="I429" t="s">
         <v>36</v>
       </c>
-      <c r="J429" t="s">
+      <c r="J429" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="K429" t="s">
-        <v>34</v>
-      </c>
-      <c r="L429" t="s">
+      <c r="K429" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L429" s="5" t="s">
         <v>76</v>
       </c>
       <c r="M429" s="4">
@@ -42993,7 +43017,7 @@
       <c r="X458">
         <v>0</v>
       </c>
-      <c r="Y458">
+      <c r="Y458" s="8">
         <v>36000</v>
       </c>
       <c r="AE458" s="4">
@@ -43060,7 +43084,7 @@
       <c r="X459">
         <v>0</v>
       </c>
-      <c r="Y459">
+      <c r="Y459" s="8">
         <v>13000</v>
       </c>
       <c r="AE459" s="4">
@@ -43127,7 +43151,7 @@
       <c r="X460">
         <v>0</v>
       </c>
-      <c r="Y460">
+      <c r="Y460" s="8">
         <v>12000</v>
       </c>
       <c r="AE460" s="4">
@@ -43194,7 +43218,7 @@
       <c r="X461">
         <v>0</v>
       </c>
-      <c r="Y461">
+      <c r="Y461" s="8">
         <v>13000</v>
       </c>
       <c r="AE461" s="4">
@@ -43261,7 +43285,7 @@
       <c r="X462">
         <v>0</v>
       </c>
-      <c r="Y462">
+      <c r="Y462" s="8">
         <v>13000</v>
       </c>
       <c r="AE462" s="4">
@@ -43328,7 +43352,7 @@
       <c r="X463">
         <v>0</v>
       </c>
-      <c r="Y463">
+      <c r="Y463" s="8">
         <v>15000</v>
       </c>
       <c r="AC463" t="s">
@@ -43401,7 +43425,7 @@
       <c r="X464">
         <v>0</v>
       </c>
-      <c r="Y464">
+      <c r="Y464" s="8">
         <v>15000</v>
       </c>
       <c r="AC464" t="s">
@@ -43474,7 +43498,7 @@
       <c r="X465">
         <v>0</v>
       </c>
-      <c r="Y465">
+      <c r="Y465" s="8">
         <v>15000</v>
       </c>
       <c r="AC465" t="s">
@@ -43547,7 +43571,7 @@
       <c r="X466">
         <v>0</v>
       </c>
-      <c r="Y466">
+      <c r="Y466" s="8">
         <v>14000</v>
       </c>
       <c r="AC466" t="s">
@@ -43619,7 +43643,7 @@
       <c r="X467">
         <v>0</v>
       </c>
-      <c r="Y467">
+      <c r="Y467" s="8">
         <v>14000</v>
       </c>
       <c r="AC467" t="s">
@@ -43654,6 +43678,7 @@
       <c r="G468" t="s">
         <v>106</v>
       </c>
+      <c r="H468" s="8"/>
       <c r="J468" t="s">
         <v>52</v>
       </c>
@@ -43691,7 +43716,7 @@
       <c r="X468">
         <v>0</v>
       </c>
-      <c r="Y468">
+      <c r="Y468" s="8">
         <v>14500</v>
       </c>
       <c r="AC468" t="s">
@@ -43726,6 +43751,7 @@
       <c r="G469" t="s">
         <v>106</v>
       </c>
+      <c r="H469" s="8"/>
       <c r="J469" t="s">
         <v>52</v>
       </c>
@@ -43763,7 +43789,7 @@
       <c r="X469">
         <v>0</v>
       </c>
-      <c r="Y469">
+      <c r="Y469" s="8">
         <v>15000</v>
       </c>
       <c r="AC469" t="s">
@@ -43798,6 +43824,7 @@
       <c r="G470" t="s">
         <v>106</v>
       </c>
+      <c r="H470" s="8"/>
       <c r="J470" t="s">
         <v>52</v>
       </c>
@@ -43835,7 +43862,7 @@
       <c r="X470">
         <v>0</v>
       </c>
-      <c r="Y470">
+      <c r="Y470" s="8">
         <v>15000</v>
       </c>
       <c r="AC470" t="s">
@@ -43908,7 +43935,7 @@
       <c r="X471">
         <v>0</v>
       </c>
-      <c r="Y471">
+      <c r="Y471" s="8">
         <v>13000</v>
       </c>
       <c r="AC471" t="s">
@@ -43981,7 +44008,7 @@
       <c r="X472">
         <v>0</v>
       </c>
-      <c r="Y472">
+      <c r="Y472" s="8">
         <v>36000</v>
       </c>
       <c r="AC472" t="s">
@@ -44054,7 +44081,7 @@
       <c r="X473">
         <v>0</v>
       </c>
-      <c r="Y473">
+      <c r="Y473" s="8">
         <v>13000</v>
       </c>
       <c r="AC473" t="s">
@@ -44086,7 +44113,7 @@
       <c r="C474" t="s">
         <v>44</v>
       </c>
-      <c r="G474" t="s">
+      <c r="G474" s="9" t="s">
         <v>111</v>
       </c>
       <c r="J474" t="s">
@@ -44127,7 +44154,7 @@
       <c r="X474">
         <v>0</v>
       </c>
-      <c r="Y474">
+      <c r="Y474" s="8">
         <v>10000</v>
       </c>
       <c r="AC474" t="s">
